--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-议程时间轴分工" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-应急预案" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-物资清单" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-志愿者花名册" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-志愿者实际分配" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08-志愿者联络表" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +60,13 @@
       <name val="微软雅黑"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +76,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,6 +145,28 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3136,23 +3194,926 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>志愿者花名册（请填）</t>
+          <t>志愿者实际分配（基于 2026-05-13 志愿者讨论会报名意向）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>共 25 人；偏好→实分 表示该志愿者勾选了多组、最终分配的组别</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>组别</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>岗位</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>报名意向</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>背景关键词</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>分配理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>总策划/总指挥</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Aiden（您）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>会长/总策划</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>全场最高决策，对接主办方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>执行总监/副指挥</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>李振春（春子）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>未明示</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>科创背景、会务经验、主动承担</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>经验+主动性最适合做总策划副手</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>文件秘书/经院联络</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>B/G</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>复旦经院培训负责人(退休)，时间充裕</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>经院校友资源+培训组织经验金牌秘书；G机动可随时调</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 副总指挥（B）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>蒋珊</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>AI赛道、跨校研究院、俱乐部运营</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>AI圈层资源+运营履历，最适合带 B 组主导嘉宾对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>VIP 1V1（港澳/海外）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>朱铭喆</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>B/C → B</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>友邦保险、香港城市大学上海联络人</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>港校联络人，专业形象，适合涉外/港澳嘉宾陪同</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>VIP 1V1（主旨嘉宾）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>JasonCAI 蔡杰</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>B/G → B</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>复旦MBA、设计咨询</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>MBA形象+设计审美，适合白硕、夏春等主旨嘉宾1V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>VIP 1V1（金融/投融资嘉宾）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Winny</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>B/C/F均可 → B</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>职业空窗期，时间最充裕</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>时间最充裕，可全程紧贴一位VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>机构嘉宾对接</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>吕志翔</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>12级、投融资</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>投融资人脉，对接 招行/长江证券/金浦 等机构嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>签到台主管</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>彭常丽</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>B/F+签到会务 → B</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>金融、二次参与、自报签到会务</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>已熟悉流程，自荐签到，直接做签到台总控</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>签到/动线引导</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Angi 郭杰</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>国际贸易、首次参与</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>新人友好岗位，标准化动作易上手</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>动线引导</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>标准引导岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>动线引导（备机动）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>高辰辰</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>B（听安排）</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>同浦汇、首次参与</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>明确说听安排，安排在B并打机动标，缺人时支援其他组</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 流程总控+计时</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>王珏</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>中信证券，自报会务+倒计时</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>自己主动认领倒计时，金融人严谨,适合做C组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>副组长 / 舞台引导+物料</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>广告活动一条龙、有自有设备</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>策划+广告专业，可主导舞台呈现+应急设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>主持对接/串场</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>冯墨 律师</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>C/B → C</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>刚从私募转律师，时间灵活，沟通强</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>PPT/资料对接</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>黄璐 Lucius</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>B/C → C</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>养老研究、首次参与</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>新人友好的细致岗，提前24h收齐讲者PPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>颁奖执行/嘉宾对接</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>徐胜博</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>未明示</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>一二级创投、K12教育</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>创投背景对接颁奖机构得体，主动报名安排合适岗位</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 摄影摄像+自媒体</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>张蒙 AEGISTAR</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>大宗行/房地产/AI数据中心、本身做自媒体</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>唯一自报D且本身做自媒体，天然D组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>直播+新媒体</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>皮尔德小号</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>未明示</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>互联网→城市更新、资源对接强</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>互联网经验+资源对接力，主管直播与新媒体即时发布</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>媒体接待+会后传播</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>马磊</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>未明示</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>跨界生态融入</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>跨界资源+对外沟通，负责财经/科技媒体接待</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>技术总监(志愿端)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>随圣博 Joshua-Sui</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>B/E/G → E</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>—（自荐E）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>唯一勾选E的志愿者，对接场馆AV外包团队即可</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 场地+物料</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>19级、建筑+市场开发、复旦网球协会运营</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>建筑专业+协会长期运营，最熟物料/场地落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>副组长 / 茶歇+晚宴</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>王胜（20级）</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>B/F → F</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>第三次参加，资深</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>三次参加经验最足，副组长稳盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>物料+茶歇执行</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>刘严</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>自报到F</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>明确自报F，标准执行岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 安保+机动调配</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>康诺斯 Conns</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>B/G → G</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>设计改造+碳资产</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>B/G均可的人里背景最综合，做机动组长可跨组顶人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>法务/舆情口径+机动</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>张卓 盈科</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>B/G → G</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>财税律师</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>律师身份处理舆情口径与突发法务最稳</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>志愿者联络方式（请补全）</t>
         </is>
       </c>
     </row>
@@ -3164,35 +4125,30 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>岗位</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>手机</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>微信</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>微信</t>
+          <t>到场时间</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>到场时间</t>
+          <t>应急联系人</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>应急联系人</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -3201,12 +4157,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>A 统筹协调组</t>
+          <t>A - 总策划/总指挥</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>总指挥</t>
+          <t>Aiden（您）</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -3214,17 +4170,16 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A 统筹协调组</t>
+          <t>A - 执行总监/副指挥</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>执行调度</t>
+          <t>李振春（春子）</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -3232,17 +4187,16 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A 统筹协调组</t>
+          <t>A - 文件秘书/经院联络</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>文件秘书</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -3250,17 +4204,16 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - 组长 / 副总指挥（B）</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>VIP一对一</t>
+          <t>蒋珊</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -3268,17 +4221,16 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - VIP 1V1（港澳/海外）</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>机场/酒店接送</t>
+          <t>朱铭喆</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
@@ -3286,17 +4238,16 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - VIP 1V1（主旨嘉宾）</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>签到台</t>
+          <t>JasonCAI 蔡杰</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
@@ -3304,17 +4255,16 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - VIP 1V1（金融/投融资嘉宾）</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>引导动线</t>
+          <t>Winny</t>
         </is>
       </c>
       <c r="C10" s="5" t="n"/>
@@ -3322,17 +4272,16 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - 机构嘉宾对接</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>休息室管理</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -3340,17 +4289,16 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>B 嘉宾接待组</t>
+          <t>B - 签到台主管</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>名片/合影</t>
+          <t>彭常丽</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -3358,17 +4306,16 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>B - 签到/动线引导</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>流程总控</t>
+          <t>Angi 郭杰</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -3376,17 +4323,16 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>B - 动线引导</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>舞台引导</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -3394,17 +4340,16 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>B - 动线引导（备机动）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>计时员</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -3412,17 +4357,16 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>C - 组长 / 流程总控+计时</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>主持对接</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -3430,17 +4374,16 @@
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>C - 副组长 / 舞台引导+物料</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -3448,17 +4391,16 @@
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C 会务执行组</t>
+          <t>C - 主持对接/串场</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -3466,17 +4408,16 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>D 媒体宣传组</t>
+          <t>C - PPT/资料对接</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -3484,17 +4425,16 @@
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>D 媒体宣传组</t>
+          <t>C - 颁奖执行/嘉宾对接</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>直播/录播</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -3502,17 +4442,16 @@
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>D 媒体宣传组</t>
+          <t>D - 组长 / 摄影摄像+自媒体</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>媒体接待</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -3520,17 +4459,16 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>D 媒体宣传组</t>
+          <t>D - 直播+新媒体</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新媒体即时发布</t>
+          <t>皮尔德小号</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -3538,17 +4476,16 @@
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>D 媒体宣传组</t>
+          <t>D - 媒体接待+会后传播</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>会后传播</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -3556,17 +4493,16 @@
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>E - 技术总监(志愿端)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>音响/麦克风</t>
+          <t>随圣博 Joshua-Sui</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -3574,17 +4510,16 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>F - 组长 / 场地+物料</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>PPT切换/总控</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -3592,17 +4527,16 @@
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>F - 副组长 / 茶歇+晚宴</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>灯光</t>
+          <t>王胜（20级）</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -3610,17 +4544,16 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>F - 物料+茶歇执行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>LED大屏/字幕</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -3628,17 +4561,16 @@
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>G - 组长 / 安保+机动调配</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>网络/直播</t>
+          <t>康诺斯 Conns</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -3646,17 +4578,16 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>E 技术支持组</t>
+          <t>G - 法务/舆情口径+机动</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>应急备件</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -3664,209 +4595,10 @@
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>场地/桌椅</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>物料制作</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>茶歇/饮水</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>伴手礼</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>交响乐团对接</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>F 后勤保障组</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>VIP晚宴</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>G 应急安全组</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>入场安检</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>G 应急安全组</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>现场巡视</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>G 应急安全组</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>医疗急救</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>G 应急安全组</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>舆情/口径</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>G 应急安全组</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>VIP/晚宴安保</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -15,6 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-物资清单" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07-志愿者实际分配" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08-志愿者联络表" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09-优化建议筛选" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10-Milestone时间表" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11-嘉宾时间控制SOP" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-对接联系人清单" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-组长AB角备份" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-核心策划圈" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +71,14 @@
       <color rgb="00808080"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +120,11 @@
         <fgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -135,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +183,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -847,6 +867,1305 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Milestone 时间表（采纳韦佳玉建议：所有节点提前 1-2 天）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>时间节点</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>关键里程碑</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>T-9 (5/13)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>志愿者讨论会完成→分工表发布（已完成）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>T-8 (5/14)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>各组建独立沟通群+组长 A/B 角确定+核心策划圈群</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>A+各组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>T-8 (5/14)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>组长见面会（线上 1h）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>A+组长</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>T-7 (5/15)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>晚宴名单锁定 V1（去年痛点：太晚锁定）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>B+F</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>T-7 (5/15)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>交响乐往届视频开始日更预热（视频号）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>T-7 (5/15)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>现场踏勘 1（场地/动线/AV）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>A+C+E+F</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>T-5 (5/17)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>所有讲者 PPT 截稿（去年是 T-3，今年提前）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>T-5 (5/17)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>地铁→场地快进短视频拍摄完成</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>D+F</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>T-5 (5/17)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>物料/胸牌印刷下单（去年痛点：名牌制作晚）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>T-4 (5/18)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>腾讯/华为赞助物料对接清单确认</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>F+A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>T-3 (5/19)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>T-3 (5/19)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>T-3 (5/19)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>短视频发主群+嘉宾群预热</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>T-2 (5/20)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>T-2 (5/20)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>现场踏勘 2（含彩排站位）</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>A+C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>全员线上彩排 18:00-19:30（1.5h）</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>A+全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>全设备压力测试+陈潇工厂设备进场</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>T-0 09:00</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>现场指挥部成立、对讲机分发、AED/急救包就位</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>A+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>T-0 12:00</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>签到台开台、VIP 车队首班、直播试推流</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>B+D</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>T-0 13:25</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>全员就位静默 5 分钟、广播开场倒计时</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>T+1</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>通稿次日 10:00 前发布、复盘会、问题归档</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>A+D</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>嘉宾发言时间控制 SOP（去年最大事故：从第 1 位讲者就开始超时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>时间点</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>动作</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>T-7</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>整理每位讲者的演讲时长合同/邀约函（25/20/40min）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>C 组致电每位讲者：再次确认时长 + 提示我们会举牌</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>C 组与 4 位主持人对脚本：嘉宾超时由你直接打断的话术</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>T-1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>彩排时给主持人发『收口话术卡』：'感谢XXX，最后一分钟'</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>T-0 演讲前 2min</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>计时员就位，倒计时牌(5/3/1 min)摆放台口</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>T-0 演讲中 5/3/1min</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>在嘉宾视线方向举牌（先黄后红）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>T-0 超时 30s</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>主持人通过耳麦提示'最后一句话'</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>T-0 超时 90s</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>主持人直接收口：'感谢XXX的精彩分享'走流程</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>T-0 圆桌嘉宾</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>每人剩 1min 时主持人示意；超时立即转下一位</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>协助人员对接清单（解决『事事请示总策划』瓶颈，全员人手一份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>采纳张卓建议：现场遇到问题先找对应志愿者，找不到再找 B 角，最后才找韦佳玉/Aiden</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>问题类别 / 你遇到的事情</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>找谁（A 角）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>找不到时（B 角）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>场地/桌椅/灯光</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>F 组 朱俊峰</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>C 组 陈潇 Kelly（自有设备）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>音响/麦克风/PPT/直播</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>E 组 随圣博</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>C 组 陈潇 Kelly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>酒店/嘉宾接送/休息室</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>B 组 蒋珊</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（A 组）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>VIP 嘉宾临时需求</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>B 组对应 1V1 责任人</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>蒋珊（B 组长）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>茶歇/餐饮/伴手礼</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>F 组 王胜</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>刘严</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>赞助物料（腾讯/华为）</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>F 组 刘严</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>摄影/摄像/直播信号</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>D 组 张蒙</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>皮尔德小号</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>媒体/记者接待</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>D 组 马磊</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>讲者 PPT/资料/换片</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>C 组 黄璐</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>流程超时/嘉宾迟到</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>C 组 王珏</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>颁奖物料/获奖嘉宾</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>C 组 徐胜博</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>王珏</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>法务/舆情/突发声明</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>G 组 张卓</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>医疗/急救</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>G 组 蔡萍 ★</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>G 组 康诺斯</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>跨组人手不足</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>G 组 康诺斯</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>交响乐团对接</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>F 组 朱俊峰</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（去年负责）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>晚宴席位/敬酒/现场对接</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>F 组 王胜</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>B 组 蒋珊</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>无法解决/重大决策</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉 → Aiden</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>组长 A/B 角备份制度（采纳王胜建议：应对组长当天缺席）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>组</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>A 角组长</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>B 角备份</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>A 统筹</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Aiden 缺席由韦佳玉全权代行</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>B 接待</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>蒋珊</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>朱铭喆</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>B 角熟悉 VIP 接待流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C 会务</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>王珏</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>B 角有活动策划 20 年经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>张蒙 AEGISTAR</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>皮尔德小号</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>B 角有互联网+直播经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>E 技术</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>随圣博</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>B 角持有自有设备，可顶上</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>F 后勤</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>王胜</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>B 角第三次参加最熟流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>G 应急</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>康诺斯</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>张卓</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>B 角律师可应对突发</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>核心策划圈（Aiden 5/13 会上点名的高频沟通小圈子，6 人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>在分工表中的角色</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>在核心圈的作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Aiden（您）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>总策划</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>全场指挥</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>执行总监</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>副总策划，统筹各组</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Winny 温妮</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>B 组VIP</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>空窗期可承担时间敏感任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>C 组副组长</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>提供灯光/舞台/音响设备资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>王胜</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>F 组副组长</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>三次参加，老带新</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>李振春 春子</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A 组秘书</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>科创资源对接（赞助/展位）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2704,7 +4023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2771,7 +4090,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>T-3 印刷完成</t>
+          <t>T-5 印刷完成（前移）</t>
         </is>
       </c>
     </row>
@@ -2798,7 +4117,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>T-1 完成</t>
+          <t>T-2 完成（去年痛点：太晚）</t>
         </is>
       </c>
     </row>
@@ -2810,22 +4129,22 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>签到表/电子签到</t>
+          <t>★志愿者专用橙色胸牌</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>分级 4 类</t>
+          <t>26 张（含韦佳玉）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>F+B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>当日 12:00 上线</t>
+          <t>T-2 完成（采纳张蒙建议）</t>
         </is>
       </c>
     </row>
@@ -2837,49 +4156,49 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>横幅/KT板/引导牌</t>
+          <t>签到表/电子签到</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>全场</t>
+          <t>分级 4 类</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F+B</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>当日 10:00 前</t>
+          <t>当日 12:00 上线</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>手持麦×4 / 领夹麦×4</t>
+          <t>横幅/KT板/引导牌</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>各 2 备用</t>
+          <t>全场</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>当日 10:00 测试</t>
+          <t>当日 10:00 前</t>
         </is>
       </c>
     </row>
@@ -2891,12 +4210,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>翻页器×4 / 备用电脑×1</t>
+          <t>手持麦×4 / 领夹麦×4</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>各 2 备用</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2906,7 +4225,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>T-1 检查</t>
+          <t>当日 10:00 测试</t>
         </is>
       </c>
     </row>
@@ -2918,12 +4237,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>转接头/线材</t>
+          <t>翻页器×4 / 备用电脑×1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>HDMI/Type-C/Lightning 各 3</t>
+          <t>——</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2933,7 +4252,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>T-1</t>
+          <t>T-1 检查</t>
         </is>
       </c>
     </row>
@@ -2945,238 +4264,454 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>对讲机</t>
+          <t>转接头/线材</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>20 台（分 3 频道）</t>
+          <t>HDMI/Type-C/Lightning 各 3</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>A+E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>当日 09:00 分发</t>
+          <t>T-1</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像机</t>
+          <t>对讲机</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>主机×2 游机×2</t>
+          <t>26 台（分 3 频道）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+E</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>当日 11:00 调试</t>
+          <t>当日 09:00 分发</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>直播推流设备</t>
+          <t>★陈潇张江工厂灯光/舞台/音响</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>1 套（含备用 4G）</t>
+          <t>1 套（自有资源）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>D+E</t>
+          <t>C+E</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>T-1 试推</t>
+          <t>T-1 进场（陈潇主导，节省赞助）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>茶歇（500人）</t>
+          <t>摄影/摄像机</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>高端冷餐/茶饮</t>
+          <t>主机×2 游机×2</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>15:30 上桌</t>
+          <t>当日 11:00 调试</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>伴手礼</t>
+          <t>直播推流设备</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>VVIP/嘉宾/机构 3 档</t>
+          <t>1 套（含备用 4G）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D+E</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>T-1 分装</t>
+          <t>T-1 试推（直播确认开启）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>晚宴桌花/席位卡</t>
+          <t>★地铁→场地快进短视频</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>500 人 50 桌</t>
+          <t>1 段 60 秒</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D+F</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>18:00 前完成</t>
+          <t>T-5 拍摄完成、T-3 群发</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>急救包/AED 标识</t>
+          <t>★交响乐往届预热视频</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2 套 / 全场 3 处</t>
+          <t>5-7 段 短视频</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>当日 09:00 就位</t>
+          <t>T-7 起视频号每日 1 条</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>后勤</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>应急联络卡</t>
+          <t>茶歇（500人）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>全员人手 1 张</t>
+          <t>高端冷餐/茶饮</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>A+G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>T-1 发放</t>
+          <t>15:30 上桌</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>伴手礼</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>VVIP/嘉宾/机构 3 档</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>T-2 分装（前移）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>晚宴桌花/席位卡</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>500 人 50 桌</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>18:00 前完成（晚宴名单 T-7 锁定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>★赞助物料（腾讯/华为）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>按合同清单</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>T-4 与品牌方对接确认（去年痛点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>志愿者午餐+证书+纪念品</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>26 套</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>A+F</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>T-1 分装、当日 12:00 发</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>应急</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>急救包/AED 标识</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2 套 / 全场 3 处</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>当日 09:00 就位</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>★急救主岗（蔡萍持证）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>1 名</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>全程在 G 组指挥点待命</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>应急联络卡（含对接清单）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>全员人手 1 张</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>A+G</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>T-3 发放（采纳张卓建议）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>备用雨伞</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>100 把</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>视天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>★T-2 嘉宾点对点提醒短信/微信</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>全部嘉宾</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>T-2 18:00 前完成（采纳JasonCAI建议）</t>
         </is>
       </c>
     </row>
@@ -3194,7 +4729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3279,7 +4814,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>全场最高决策，对接主办方</t>
+          <t>全场最高决策，对接主办方与赞助方（腾讯/华为）</t>
         </is>
       </c>
     </row>
@@ -3291,27 +4826,27 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>执行总监/副指挥</t>
+          <t>执行总监/副总策划</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>李振春（春子）</t>
+          <t>韦佳玉</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>—（Aiden 直接点名协助统筹）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>科创背景、会务经验、主动承担</t>
+          <t>23级校友、股权一级市场投融资、参与多届</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>经验+主动性最适合做总策划副手</t>
+          <t>Aiden会上直接点名协助总策划；多届经验+资源整合，最适合做总策划副手</t>
         </is>
       </c>
     </row>
@@ -3323,27 +4858,27 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>文件秘书/经院联络</t>
+          <t>文件秘书/科创联络</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>李振春（春子）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>B/G</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>复旦经院培训负责人(退休)，时间充裕</t>
+          <t>经院校友、科创业务、有会务/签到经验</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>经院校友资源+培训组织经验金牌秘书；G机动可随时调</t>
+          <t>主动承担+科创资源（可对接科技展示赞助）</t>
         </is>
       </c>
     </row>
@@ -3355,7 +4890,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>组长 / 副总指挥（B）</t>
+          <t>组长</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3375,7 +4910,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>AI圈层资源+运营履历，最适合带 B 组主导嘉宾对接</t>
+          <t>AI圈层资源+运营履历最适合带 B 组主导嘉宾对接</t>
         </is>
       </c>
     </row>
@@ -3387,7 +4922,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>VIP 1V1（港澳/海外）</t>
+          <t>VIP 1V1（港澳/海外嘉宾）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3407,7 +4942,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>港校联络人，专业形象，适合涉外/港澳嘉宾陪同</t>
+          <t>港校联络人，专业形象+沟通能力，适合涉外/港澳嘉宾</t>
         </is>
       </c>
     </row>
@@ -3439,7 +4974,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>MBA形象+设计审美，适合白硕、夏春等主旨嘉宾1V1</t>
+          <t>形象气质+审美佳，适合白硕、夏春等主旨嘉宾</t>
         </is>
       </c>
     </row>
@@ -3451,7 +4986,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>VIP 1V1（金融/投融资嘉宾）</t>
+          <t>VIP 1V1（核心搭子）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3466,12 +5001,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>职业空窗期，时间最充裕</t>
+          <t>空窗期时间最充裕、IP授权运营</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>时间最充裕，可全程紧贴一位VIP</t>
+          <t>时间最充裕可全程紧贴VIP；Aiden 核心搭子之一</t>
         </is>
       </c>
     </row>
@@ -3498,12 +5033,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>12级、投融资</t>
+          <t>12级、投融资、教育/医疗/AI</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>投融资人脉，对接 招行/长江证券/金浦 等机构嘉宾</t>
+          <t>投融资人脉，对接 招行/长江证券/金浦 等机构</t>
         </is>
       </c>
     </row>
@@ -3530,12 +5065,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>金融、二次参与、自报签到会务</t>
+          <t>金融、二次参与、自报签到</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>已熟悉流程，自荐签到，直接做签到台总控</t>
+          <t>二次参与已熟悉流程，签到台总控</t>
         </is>
       </c>
     </row>
@@ -3547,7 +5082,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>签到/动线引导</t>
+          <t>观众席引导（新增岗）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -3562,12 +5097,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>国际贸易、首次参与</t>
+          <t>国际贸易、首次</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新人友好岗位，标准化动作易上手</t>
+          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
         </is>
       </c>
     </row>
@@ -3611,7 +5146,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>动线引导（备机动）</t>
+          <t>动线引导/机动</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -3626,12 +5161,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>同浦汇、首次参与</t>
+          <t>同浦汇、首次</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>明确说听安排，安排在B并打机动标，缺人时支援其他组</t>
+          <t>明确说听安排，B岗+机动标，缺人时支援</t>
         </is>
       </c>
     </row>
@@ -3663,7 +5198,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>自己主动认领倒计时，金融人严谨,适合做C组长</t>
+          <t>自荐倒计时，金融严谨适合 C 组长</t>
         </is>
       </c>
     </row>
@@ -3675,7 +5210,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 舞台引导+物料</t>
+          <t>副组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3690,12 +5225,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>广告活动一条龙、有自有设备</t>
+          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、Aiden 核心搭子</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>策划+广告专业，可主导舞台呈现+应急设备</t>
+          <t>重大资源：可提供专业灯光/舞台/音响设备，副组长兼设备总管</t>
         </is>
       </c>
     </row>
@@ -3722,7 +5257,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>刚从私募转律师，时间灵活，沟通强</t>
+          <t>私募→律师、时间灵活、沟通强</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -3754,12 +5289,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>养老研究、首次参与</t>
+          <t>建筑设计+地产+养老研究、首次</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>新人友好的细致岗，提前24h收齐讲者PPT</t>
+          <t>细致岗，提前 24h 收齐讲者 PPT</t>
         </is>
       </c>
     </row>
@@ -3771,7 +5306,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行/嘉宾对接</t>
+          <t>颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -3791,7 +5326,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>创投背景对接颁奖机构得体，主动报名安排合适岗位</t>
+          <t>创投背景对接颁奖机构得体</t>
         </is>
       </c>
     </row>
@@ -3818,12 +5353,12 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>大宗行/房地产/AI数据中心、本身做自媒体</t>
+          <t>大宗行/AI数据中心、本身做自媒体</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>唯一自报D且本身做自媒体，天然D组长</t>
+          <t>唯一自报 D 且本身做自媒体，天然 D 组长</t>
         </is>
       </c>
     </row>
@@ -3835,7 +5370,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>直播+新媒体</t>
+          <t>直播+新媒体（含交响乐预热）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3850,12 +5385,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>互联网→城市更新、资源对接强</t>
+          <t>互联网 10 年→城市更新、资源对接强</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>互联网经验+资源对接力，主管直播与新媒体即时发布</t>
+          <t>互联网经验+资源对接力，主管直播与新媒体；负责交响乐往届视频在视频号 T-7 起每日预热</t>
         </is>
       </c>
     </row>
@@ -3882,12 +5417,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>跨界生态融入</t>
+          <t>AI Club 生态、跨界资源</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>跨界资源+对外沟通，负责财经/科技媒体接待</t>
+          <t>跨界资源+AI 圈层人脉，对接财经/科技媒体</t>
         </is>
       </c>
     </row>
@@ -3899,7 +5434,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>技术总监(志愿端)</t>
+          <t>技术对接（志愿端）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3914,12 +5449,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>—（自荐E）</t>
+          <t>复旦管院年会后勤经验</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>唯一勾选E的志愿者，对接场馆AV外包团队即可</t>
+          <t>唯一勾选 E 的志愿者，对接场馆 AV 外包+陈潇张江工厂设备</t>
         </is>
       </c>
     </row>
@@ -3963,7 +5498,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 茶歇+晚宴</t>
+          <t>副组长 / 茶歇+晚宴+核心搭子</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3978,12 +5513,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第三次参加，资深</t>
+          <t>第三次参加，资深；Aiden 核心搭子</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>三次参加经验最足，副组长稳盘</t>
+          <t>三次参加经验最足；Aiden 核心搭子，副组长稳盘</t>
         </is>
       </c>
     </row>
@@ -3995,7 +5530,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>物料+茶歇执行</t>
+          <t>物料+伴手礼+赞助物料对接</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -4010,12 +5545,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>自报到F</t>
+          <t>自报到F、平日接活多</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>明确自报F，标准执行岗</t>
+          <t>自报 F；负责对接腾讯/华为赞助物料入场（去年痛点）</t>
         </is>
       </c>
     </row>
@@ -4042,12 +5577,12 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>设计改造+碳资产</t>
+          <t>设计改造+碳资产、首次</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>B/G均可的人里背景最综合，做机动组长可跨组顶人</t>
+          <t>做机动组长可跨组顶人</t>
         </is>
       </c>
     </row>
@@ -4059,7 +5594,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>法务/舆情口径+机动</t>
+          <t>法务/舆情口径</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -4074,12 +5609,44 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>财税律师</t>
+          <t>财税律师、二次参加</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>律师身份处理舆情口径与突发法务最稳</t>
+          <t>律师处理舆情口径与突发法务最稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>急救/医疗主岗 ★</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>B/G → G</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>复旦经院培训负责人(退休)、★持有急救证</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>★稀缺技能：自报有急救证；G 组急救/医疗专项岗，会议突发医疗60秒响应</t>
         </is>
       </c>
     </row>
@@ -4098,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4174,12 +5741,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A - 执行总监/副指挥</t>
+          <t>A - 执行总监/副总策划</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>李振春（春子）</t>
+          <t>韦佳玉</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -4191,12 +5758,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A - 文件秘书/经院联络</t>
+          <t>A - 文件秘书/科创联络</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>李振春（春子）</t>
         </is>
       </c>
       <c r="C6" s="5" t="n"/>
@@ -4208,7 +5775,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>B - 组长 / 副总指挥（B）</t>
+          <t>B - 组长</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4225,7 +5792,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>B - VIP 1V1（港澳/海外）</t>
+          <t>B - VIP 1V1（港澳/海外嘉宾）</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -4259,7 +5826,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B - VIP 1V1（金融/投融资嘉宾）</t>
+          <t>B - VIP 1V1（核心搭子）</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -4310,7 +5877,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>B - 签到/动线引导</t>
+          <t>B - 观众席引导（新增岗）</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4344,7 +5911,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>B - 动线引导（备机动）</t>
+          <t>B - 动线引导/机动</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -4378,7 +5945,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C - 副组长 / 舞台引导+物料</t>
+          <t>C - 副组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -4429,7 +5996,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>C - 颁奖执行/嘉宾对接</t>
+          <t>C - 颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -4463,7 +6030,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>D - 直播+新媒体</t>
+          <t>D - 直播+新媒体（含交响乐预热）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -4497,7 +6064,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>E - 技术总监(志愿端)</t>
+          <t>E - 技术对接（志愿端）</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -4531,7 +6098,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>F - 副组长 / 茶歇+晚宴</t>
+          <t>F - 副组长 / 茶歇+晚宴+核心搭子</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4548,7 +6115,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>F - 物料+茶歇执行</t>
+          <t>F - 物料+伴手礼+赞助物料对接</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -4582,7 +6149,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>G - 法务/舆情口径+机动</t>
+          <t>G - 法务/舆情口径</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -4595,6 +6162,23 @@
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="G29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>G - 急救/医疗主岗 ★</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4602,4 +6186,583 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>5/13 志愿者讨论会  19 条建议筛选与处置</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>处置：采纳 / 调整后采纳 / 暂缓（暂缓 = 经判断不进 5/22 必交付，但不否定其价值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>建议人</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>建议内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>处置</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>落地动作</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>量化各组任务量+设置 Milestone（按时间精力选岗位）</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>新增 Milestone 表（见 09 sheet），各组组长 T-7 前提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>所有 Milestone 节点提前 1-2 天，留 buffer</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>阶段任务矩阵已整体前移，T-3 改为 T-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>张卓</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>提前半天/线上彩排，明确工作范围边界</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>A+全员</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>T-1 18:00 全员线上彩排 1.5h；T-7 现场踏勘 1 次</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>张卓</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>协助人员对接清单（酒店/屏幕谁联系，避免事事请示总策划）</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>新增 11-对接联系人清单（见 sheet），人手一份</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>张卓</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>嘉宾发言时间提前打招呼+主持人收口</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>C 组 T-3 致电每位讲者+主持人对脚本（见 10-嘉宾时间SOP）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>春子</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>增加科技类展示（AI/机器人/芯片小海报）</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>暂缓→单列待办</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>需赞助谈判，春子+Aiden 私下推进，不进 5/22 必交付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>蒋珊</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>扩大交响乐宣传，视频号发去年录像预告</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>D 组皮尔德小号负责，T-7 起每日 1 条；T-3 集中投流</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>蒋珊</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>演奏者走位与观众互动</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>暂缓</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Aiden 已明确专业度不足；现场仅做灯光烘托</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>隋胜博/徐胜博</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>地铁→场地快进短视频群发</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>D+F</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>T-5 拍摄、T-3 发群（去年已做，今年延续）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>JasonCAI</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>T-2 微信+短信点对点提醒嘉宾交通/停车</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>B 组 VIP 1V1 责任人 T-2 18:00 前完成全部联络</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>王胜</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>组长 A/B 角备份制度</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>新增 12-组长备份表（见 sheet）每组指定 B 角</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>康诺斯</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>B 组按身高/年龄筛选</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>调整后采纳</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>改为按英语/沟通/形象气质匹配 VIP 1V1，避免歧视</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>张蒙</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>志愿者专用颜色胸牌快速识别</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>F 组制作橙色胸牌（与嘉宾胸卡明显区分），见物资清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>冯墨</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>现场观众管理（盲区）</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>B+G</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>B 组 Angi 改为观众席引导岗；G 组机动支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>自报有急救证</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍调到 G 组任急救/医疗主岗（稀缺技能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>陈潇</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>张江工厂提供灯光/舞台/音响设备</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>作为重大物料资源并入；C 组陈潇为设备总管，E 组对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>彭常丽</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>去年赞助物料环节混乱，要提前深化</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>F 组刘严专项负责赞助物料入场+点位</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Aiden确认</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>工作装+合影+证书+午餐+纪念品</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>A+F</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>已写入物资清单；T-1 全员告知</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Aiden确认</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>核心搭子：韦佳玉/Winnie/陈潇/王胜</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>建立核心策划圈高频沟通群（6 人）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>执行总监（总策划副手）</t>
+          <t>韦佳玉（执行总监）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2-3 人</t>
+          <t>3 人</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>VIP接待主管</t>
+          <t>王胜（组长）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>8-12 人</t>
+          <t>6 人</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>会务总监</t>
+          <t>陈潇 Kelly（组长）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>6-8 人</t>
+          <t>5 人</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宣传总监</t>
+          <t>葛九明（组长）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>5-7 人</t>
+          <t>5 人</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>技术总监（含场地AV团队）</t>
+          <t>随圣博（组长）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>4-6 人</t>
+          <t>3 人</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>后勤主管</t>
+          <t>朱俊峰（组长）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>5-8 人</t>
+          <t>3 人</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>应急安全组</t>
+          <t>应急安全/机动组</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>安全主管</t>
+          <t>康诺斯（组长）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>3-5 人</t>
+          <t>3 人</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1493,7 +1493,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>采纳张卓建议：现场遇到问题先找对应志愿者，找不到再找 B 角，最后才找韦佳玉/Aiden</t>
+          <t>采纳张卓建议：现场遇到问题先找对应志愿者，找不到再找 B 角，最后才找韦佳玉/胡继刚</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>场地/桌椅/灯光</t>
+          <t>场地/桌椅</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1527,277 +1527,362 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>C 组 陈潇 Kelly（自有设备）</t>
+          <t>F 组 刘严</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>音响/麦克风/PPT/直播</t>
+          <t>灯光/舞台/音响（自有）</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>C 组 陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>E 组 随圣博</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>C 组 陈潇 Kelly</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>酒店/嘉宾接送/休息室</t>
+          <t>麦克风/PPT切换/网络/直播</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>B 组 蒋珊</t>
+          <t>E 组 随圣博</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉（A 组）</t>
+          <t>E 组 高辰辰</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>VIP 嘉宾临时需求</t>
+          <t>技术赞助/腾讯华为技术对接</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>B 组对应 1V1 责任人</t>
+          <t>E 组 吕志翔</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蒋珊（B 组长）</t>
+          <t>胡继刚（总策划）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>茶歇/餐饮/伴手礼</t>
+          <t>酒店/嘉宾接送/休息室</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>F 组 王胜</t>
+          <t>B 组 王胜</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>韦佳玉（A 组）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>赞助物料（腾讯/华为）</t>
+          <t>VIP 嘉宾临时需求</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>F 组 刘严</t>
+          <t>B 组对应 1V1 责任人</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>王胜（B 组长）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像/直播信号</t>
+          <t>观众席引导/秩序</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>D 组 张蒙</t>
+          <t>B 组 Angi</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>皮尔德小号</t>
+          <t>B 组 LV / G 组 康诺斯</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>媒体/记者接待</t>
+          <t>茶歇/晚宴</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>D 组 马磊</t>
+          <t>F 组 彭常丽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>张蒙</t>
+          <t>F 组 朱俊峰</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>讲者 PPT/资料/换片</t>
+          <t>赞助物料（腾讯/华为）</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>C 组 黄璐</t>
+          <t>F 组 刘严</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>胡继刚</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>流程超时/嘉宾迟到</t>
+          <t>摄影/摄像</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>C 组 王珏</t>
+          <t>D 组 张蒙</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>葛九明（D 组长）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>颁奖物料/获奖嘉宾</t>
+          <t>直播信号/新媒体即时发布</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>C 组 徐胜博</t>
+          <t>D 组 皮尔德小号</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>蒋珊（AI 内容）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>法务/舆情/突发声明</t>
+          <t>AI 圈层金句/新媒体素材</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>G 组 张卓</t>
+          <t>D 组 蒋珊</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>马磊</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>医疗/急救</t>
+          <t>媒体/记者接待</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>G 组 蔡萍 ★</t>
+          <t>D 组 马磊</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯</t>
+          <t>葛九明</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>跨组人手不足</t>
+          <t>讲者 PPT/资料/换片</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯</t>
+          <t>C 组 黄璐</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>交响乐团对接</t>
+          <t>流程超时/嘉宾迟到</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>F 组 朱俊峰</t>
+          <t>C 组 王珏（计时）</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉（去年负责）</t>
+          <t>陈潇（C 组长）→ 韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>晚宴席位/敬酒/现场对接</t>
+          <t>颁奖物料/获奖嘉宾</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>F 组 王胜</t>
+          <t>C 组 徐胜博</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>B 组 蒋珊</t>
+          <t>王珏</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>法务/舆情/突发声明</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>G 组 张卓</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>医疗/急救 ★</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>G 组 蔡萍 ★</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>G 组 康诺斯</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>跨组人手不足/机动调配</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>G 组 康诺斯</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>交响乐团对接</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>F 组 朱俊峰</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（去年负责）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>晚宴席位/敬酒/现场对接</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>F 组 彭常丽</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>B 组 王胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>无法解决/重大决策</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>韦佳玉 → Aiden</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉 → 胡继刚</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1864,7 +1949,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>胡继刚（总策划）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1874,7 +1959,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Aiden 缺席由韦佳玉全权代行</t>
+          <t>总策划缺席由韦佳玉全权代行</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1971,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>蒋珊</t>
+          <t>王胜</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1896,7 +1981,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>B 角熟悉 VIP 接待流程</t>
+          <t>A 角第三次参加最资深；B 角港校联络人</t>
         </is>
       </c>
     </row>
@@ -1908,17 +1993,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>陈潇 Kelly</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
           <t>王珏</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>陈潇 Kelly</t>
-        </is>
-      </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>B 角有活动策划 20 年经验</t>
+          <t>A 角 20 年策划经验+设备；B 角中信证券计时主控</t>
         </is>
       </c>
     </row>
@@ -1930,17 +2015,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>葛九明</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>张蒙 AEGISTAR</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>皮尔德小号</t>
-        </is>
-      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>B 角有互联网+直播经验</t>
+          <t>A 角总策划指定；B 角自媒体+摄影核心岗</t>
         </is>
       </c>
     </row>
@@ -1957,12 +2042,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>B 角持有自有设备，可顶上</t>
+          <t>B 角投融资人脉对接技术赞助方</t>
         </is>
       </c>
     </row>
@@ -1979,12 +2064,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>王胜</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>B 角第三次参加最熟流程</t>
+          <t>A 角建筑+协会运营；B 角对接赞助物料</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2091,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>B 角律师可应对突发</t>
+          <t>B 角律师可应对突发；蔡萍持急救证常驻医疗岗</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2035,7 +2120,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>核心策划圈（Aiden 5/13 会上点名的高频沟通小圈子，6 人）</t>
+          <t>核心策划圈（总策划 5/13 点名的高频沟通小圈子 + 葛九明，共 7 人）</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2144,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Aiden（您）</t>
+          <t>胡继刚（您）</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2081,7 +2166,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>执行总监</t>
+          <t>A 执行总监</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2093,66 +2178,83 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Winny 温妮</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>B 组VIP</t>
+          <t>C 组组长</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>空窗期可承担时间敏感任务</t>
+          <t>提供灯光/舞台/音响设备资源</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王胜</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>C 组副组长</t>
+          <t>B 组组长</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>提供灯光/舞台/音响设备资源</t>
+          <t>三次参加，老带新</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>王胜</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>F 组副组长</t>
+          <t>D 组组长</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>三次参加，老带新</t>
+          <t>总策划指定，统筹媒体宣传</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>Winny 温妮</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>B 组 VIP</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>空窗期可承担时间敏感任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>李振春 春子</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>A 组秘书</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>科创资源对接（赞助/展位）</t>
         </is>
@@ -2685,7 +2787,7 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>G 应急安全组</t>
+          <t>G 应急安全/机动组</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -2841,7 +2943,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>G 应急安全组</t>
+          <t>G 应急安全/机动组</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4799,7 +4901,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Aiden（您）</t>
+          <t>胡继刚（您）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -4836,7 +4938,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>—（Aiden 直接点名协助统筹）</t>
+          <t>—（总策划点名协助统筹）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -4846,7 +4948,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Aiden会上直接点名协助总策划；多届经验+资源整合，最适合做总策划副手</t>
+          <t>总策划会上直接点名协助统筹；多届经验+资源整合</t>
         </is>
       </c>
     </row>
@@ -4895,22 +4997,22 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>蒋珊</t>
+          <t>王胜（20级）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B/F → B</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>AI赛道、跨校研究院、俱乐部运营</t>
+          <t>第三次参加最资深；原 F 副组长升任 B 组长</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>AI圈层资源+运营履历最适合带 B 组主导嘉宾对接</t>
+          <t>总策划指定升任：第三次参加经验最足，接替蒋珊带 B 组</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5108,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>时间最充裕可全程紧贴VIP；Aiden 核心搭子之一</t>
+          <t>时间最充裕可全程紧贴VIP；总策划核心搭子之一</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5120,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>机构嘉宾对接</t>
+          <t>观众席引导</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>Angi 郭杰</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -5033,12 +5135,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>12级、投融资、教育/医疗/AI</t>
+          <t>国际贸易、首次</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>投融资人脉，对接 招行/长江证券/金浦 等机构</t>
+          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
         </is>
       </c>
     </row>
@@ -5050,123 +5152,123 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>签到台主管</t>
+          <t>动线引导</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>彭常丽</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>B/F+签到会务 → B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>金融、二次参与、自报签到</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>二次参与已熟悉流程，签到台总控</t>
+          <t>标准引导岗</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>观众席引导（新增岗）</t>
+          <t>组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Angi 郭杰</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>国际贸易、首次</t>
+          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、核心搭子</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
+          <t>总策划指定升任：20年策划经验+自有设备，全场制作把关</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>动线引导</t>
+          <t>副组长 / 计时员</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>中信证券，自报会务+倒计时</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>标准引导岗</t>
+          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>动线引导/机动</t>
+          <t>主持对接/串场</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>高辰辰</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>B（听安排）</t>
+          <t>C/B → C</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>同浦汇、首次</t>
+          <t>私募→律师、时间灵活、沟通强</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>明确说听安排，B岗+机动标，缺人时支援</t>
+          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
         </is>
       </c>
     </row>
@@ -5178,27 +5280,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>组长 / 流程总控+计时</t>
+          <t>PPT/资料对接</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B/C → C</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>中信证券，自报会务+倒计时</t>
+          <t>建筑设计+地产+养老研究、首次</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>自荐倒计时，金融严谨适合 C 组长</t>
+          <t>细致岗，提前 24h 收齐讲者 PPT</t>
         </is>
       </c>
     </row>
@@ -5210,123 +5312,123 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 舞台+设备总管</t>
+          <t>颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、Aiden 核心搭子</t>
+          <t>一二级创投、K12教育</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重大资源：可提供专业灯光/舞台/音响设备，副组长兼设备总管</t>
+          <t>创投背景对接颁奖机构得体</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>主持对接/串场</t>
+          <t>组长</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>C/B → C</t>
+          <t>—（总策划指定）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>私募→律师、时间灵活、沟通强</t>
+          <t>媒体/宣传背景（待补全）</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
+          <t>总策划指定 D 组组长，统筹摄影摄像/直播/新媒体/媒体接待对外口径</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>副组长 / 摄影摄像+自媒体</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>B/C → C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>建筑设计+地产+养老研究、首次</t>
+          <t>大宗行/AI数据中心、本身做自媒体</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>细致岗，提前 24h 收齐讲者 PPT</t>
+          <t>保留摄影摄像与自媒体核心岗，作为 D 组副组长</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行/机构对接</t>
+          <t>AI 内容/新媒体（调入）</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>蒋珊</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B → D</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>一二级创投、K12教育</t>
+          <t>AI赛道、复旦人工智能俱乐部、跨校 C9 科创金融研究院</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>创投背景对接颁奖机构得体</t>
+          <t>AI 圈层资源最强；从 B 组调入做新媒体（金句卡/朋友圈/小红书）</t>
         </is>
       </c>
     </row>
@@ -5338,27 +5440,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>组长 / 摄影摄像+自媒体</t>
+          <t>直播+交响乐预热</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>皮尔德小号</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>大宗行/AI数据中心、本身做自媒体</t>
+          <t>互联网 10 年→城市更新、资源对接强</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>唯一自报 D 且本身做自媒体，天然 D 组长</t>
+          <t>主管直播；交响乐往届视频 T-7 起视频号每日预热</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5472,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>直播+新媒体（含交响乐预热）</t>
+          <t>媒体接待+会后传播</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>皮尔德小号</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -5385,44 +5487,44 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>互联网 10 年→城市更新、资源对接强</t>
+          <t>AI Club 生态、跨界资源</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>互联网经验+资源对接力，主管直播与新媒体；负责交响乐往届视频在视频号 T-7 起每日预热</t>
+          <t>跨界资源+AI 圈层人脉，对接财经/科技媒体</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>媒体接待+会后传播</t>
+          <t>组长 / 技术对接</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>随圣博 Joshua-Sui</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B/E/G → E</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>AI Club 生态、跨界资源</t>
+          <t>复旦管院年会后勤经验</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>跨界资源+AI 圈层人脉，对接财经/科技媒体</t>
+          <t>唯一勾选 E，对接场馆 AV 外包+陈潇张江工厂设备</t>
         </is>
       </c>
     </row>
@@ -5434,59 +5536,59 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>技术对接（志愿端）</t>
+          <t>技术赞助/资源对接（调入）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>随圣博 Joshua-Sui</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>B/E/G → E</t>
+          <t>B → E</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>复旦管院年会后勤经验</t>
+          <t>12级、投融资、教育/医疗/AI</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>唯一勾选 E 的志愿者，对接场馆 AV 外包+陈潇张江工厂设备</t>
+          <t>投融资人脉，对接腾讯/华为技术方+协调技术赞助资源</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>组长 / 场地+物料</t>
+          <t>技术对接助理（调入）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>朱俊峰</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B → E（听安排）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>19级、建筑+市场开发、复旦网球协会运营</t>
+          <t>同浦汇、首次</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>建筑专业+协会长期运营，最熟物料/场地落地</t>
+          <t>明确说听安排；从 B 调入做技术执行助理（标准化对接）</t>
         </is>
       </c>
     </row>
@@ -5498,27 +5600,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 茶歇+晚宴+核心搭子</t>
+          <t>组长 / 场地+物料</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>王胜（20级）</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>B/F → F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第三次参加，资深；Aiden 核心搭子</t>
+          <t>19级、建筑+市场开发、复旦网球协会运营</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>三次参加经验最足；Aiden 核心搭子，副组长稳盘</t>
+          <t>建筑专业+协会长期运营，最熟物料/场地落地</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5632,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>物料+伴手礼+赞助物料对接</t>
+          <t>副组长 / 物料+伴手礼+赞助物料</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -5550,39 +5652,39 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>自报 F；负责对接腾讯/华为赞助物料入场（去年痛点）</t>
+          <t>F 组组员升副组长；专项对接腾讯/华为赞助物料入场（去年痛点）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>组长 / 安保+机动调配</t>
+          <t>茶歇+晚宴专员（调入）</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>康诺斯 Conns</t>
+          <t>彭常丽</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>B/G → G</t>
+          <t>B/F → F</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>设计改造+碳资产、首次</t>
+          <t>金融、二次参与</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>做机动组长可跨组顶人</t>
+          <t>去年已熟悉流程，从 B 调入主管 500 人茶歇+晚宴对接</t>
         </is>
       </c>
     </row>
@@ -5594,12 +5696,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>法务/舆情口径</t>
+          <t>组长 / 安保+机动调配</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>康诺斯 Conns</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -5609,12 +5711,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>财税律师、二次参加</t>
+          <t>设计改造+碳资产、首次</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>律师处理舆情口径与突发法务最稳</t>
+          <t>做机动组长可跨组顶人</t>
         </is>
       </c>
     </row>
@@ -5626,27 +5728,59 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>副组长 / 法务+舆情口径</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>张卓 盈科</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>B/G → G</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>财税律师、二次参加</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>律师处理舆情口径与突发法务最稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
           <t>急救/医疗主岗 ★</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>蔡萍</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>B/G → G</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>复旦经院培训负责人(退休)、★持有急救证</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>★稀缺技能：自报有急救证；G 组急救/医疗专项岗，会议突发医疗60秒响应</t>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>★稀缺技能：自报有急救证；G 组急救/医疗专项岗</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5729,7 +5863,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Aiden（您）</t>
+          <t>胡继刚（您）</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -5780,7 +5914,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>蒋珊</t>
+          <t>王胜（20级）</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -5843,12 +5977,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B - 机构嘉宾对接</t>
+          <t>B - 观众席引导</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>Angi 郭杰</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -5860,12 +5994,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>B - 签到台主管</t>
+          <t>B - 动线引导</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>彭常丽</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -5877,12 +6011,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>B - 观众席引导（新增岗）</t>
+          <t>C - 组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Angi 郭杰</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -5894,12 +6028,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>B - 动线引导</t>
+          <t>C - 副组长 / 计时员</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -5911,12 +6045,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>B - 动线引导/机动</t>
+          <t>C - 主持对接/串场</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>高辰辰</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -5928,12 +6062,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C - 组长 / 流程总控+计时</t>
+          <t>C - PPT/资料对接</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -5945,12 +6079,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C - 副组长 / 舞台+设备总管</t>
+          <t>C - 颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -5962,12 +6096,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>C - 主持对接/串场</t>
+          <t>D - 组长</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -5979,12 +6113,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>C - PPT/资料对接</t>
+          <t>D - 副组长 / 摄影摄像+自媒体</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -5996,12 +6130,12 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>C - 颁奖执行/机构对接</t>
+          <t>D - AI 内容/新媒体（调入）</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>蒋珊</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -6013,12 +6147,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>D - 组长 / 摄影摄像+自媒体</t>
+          <t>D - 直播+交响乐预热</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>皮尔德小号</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -6030,12 +6164,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>D - 直播+新媒体（含交响乐预热）</t>
+          <t>D - 媒体接待+会后传播</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>皮尔德小号</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -6047,12 +6181,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>D - 媒体接待+会后传播</t>
+          <t>E - 组长 / 技术对接</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>随圣博 Joshua-Sui</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -6064,12 +6198,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>E - 技术对接（志愿端）</t>
+          <t>E - 技术赞助/资源对接（调入）</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>随圣博 Joshua-Sui</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -6081,12 +6215,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>F - 组长 / 场地+物料</t>
+          <t>E - 技术对接助理（调入）</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>朱俊峰</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -6098,12 +6232,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>F - 副组长 / 茶歇+晚宴+核心搭子</t>
+          <t>F - 组长 / 场地+物料</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>王胜（20级）</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -6115,7 +6249,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>F - 物料+伴手礼+赞助物料对接</t>
+          <t>F - 副组长 / 物料+伴手礼+赞助物料</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -6132,12 +6266,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>G - 组长 / 安保+机动调配</t>
+          <t>F - 茶歇+晚宴专员（调入）</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>康诺斯 Conns</t>
+          <t>彭常丽</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -6149,12 +6283,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>G - 法务/舆情口径</t>
+          <t>G - 组长 / 安保+机动调配</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>康诺斯 Conns</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -6166,12 +6300,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>G - 急救/医疗主岗 ★</t>
+          <t>G - 副组长 / 法务+舆情口径</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -6179,6 +6313,23 @@
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>G - 急救/医疗主岗 ★</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>蔡萍</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6403,7 +6554,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>需赞助谈判，春子+Aiden 私下推进，不进 5/22 必交付</t>
+          <t>需赞助谈判，春子+胡继刚 私下推进，不进 5/22 必交付</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6608,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Aiden 已明确专业度不足；现场仅做灯光烘托</t>
+          <t>总策划已明确专业度不足；现场仅做灯光烘托</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6858,7 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Aiden确认</t>
+          <t>总策划确认</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -6734,12 +6885,12 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Aiden确认</t>
+          <t>总策划确认</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>核心搭子：韦佳玉/Winnie/陈潇/王胜</t>
+          <t>核心搭子：韦佳玉/Winnie/陈潇/王胜+葛九明</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -6754,7 +6905,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>建立核心策划圈高频沟通群（6 人）</t>
+          <t>建立核心策划圈高频沟通群（含 D 组长葛九明 7 人）</t>
         </is>
       </c>
     </row>

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>6 人</t>
+          <t>5 人</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>5 人</t>
+          <t>6 人</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>5 人</t>
+          <t>4 人</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>随圣博（组长）</t>
+          <t>张卓（组长）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -836,12 +836,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>康诺斯（组长）</t>
+          <t>刘严（组长）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>3 人</t>
+          <t>4 人</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1517,7 +1517,7 @@
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>场地/桌椅</t>
+          <t>场地/桌椅/赞助物料入场</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>F 组 刘严</t>
+          <t>韦佳玉（A 组）</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>E 组 随圣博</t>
+          <t>E 组 张卓</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1568,17 @@
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>技术赞助/腾讯华为技术对接</t>
+          <t>E 组协调/对接外包 AV</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>E 组 吕志翔</t>
+          <t>E 组 张卓（组长）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>胡继刚（总策划）</t>
+          <t>随圣博（B 角）</t>
         </is>
       </c>
     </row>
@@ -1629,143 +1629,143 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>B 组 LV / G 组 康诺斯</t>
+          <t>G 组 康诺斯</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>茶歇/晚宴</t>
+          <t>茶歇 / 晚宴 ★</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>F 组 彭常丽</t>
+          <t>F 组 Winny（茶歇晚宴主管）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>F 组 朱俊峰</t>
+          <t>彭常丽 / 朱俊峰</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>赞助物料（腾讯/华为）</t>
+          <t>摄影/摄像</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>F 组 刘严</t>
+          <t>D 组 张蒙</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>葛九明（D 组长）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像</t>
+          <t>直播信号/新媒体即时发布</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>D 组 张蒙</t>
+          <t>D 组 皮尔德小号</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>葛九明（D 组长）</t>
+          <t>蒋珊（AI 内容）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>直播信号/新媒体即时发布</t>
+          <t>AI 圈层金句/新媒体素材</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>D 组 皮尔德小号</t>
+          <t>D 组 蒋珊</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蒋珊（AI 内容）</t>
+          <t>皮尔德小号</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>AI 圈层金句/新媒体素材</t>
+          <t>媒体/记者接待</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>D 组 蒋珊</t>
+          <t>D 组 皮尔德小号</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>葛九明</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>媒体/记者接待</t>
+          <t>讲者 PPT/资料/换片</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>D 组 马磊</t>
+          <t>C 组 黄璐</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>讲者 PPT/资料/换片</t>
+          <t>流程超时/嘉宾迟到</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>C 组 黄璐</t>
+          <t>C 组 王珏（计时）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>陈潇 → 韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>流程超时/嘉宾迟到</t>
+          <t>圆桌嘉宾上下场</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>C 组 王珏（计时）</t>
+          <t>C 组 吕志翔</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>陈潇（C 组长）→ 韦佳玉</t>
+          <t>王珏</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>G 组 张卓</t>
+          <t>C 组 冯墨（律师）</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>E 组 张卓（律师）→ 胡继刚</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯</t>
+          <t>G 组 刘严</t>
         </is>
       </c>
     </row>
@@ -1828,61 +1828,129 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯</t>
+          <t>G 组 刘严（组长）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>G 组 康诺斯 / 马磊</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>交响乐团对接</t>
+          <t>媒体应急口径</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>F 组 朱俊峰</t>
+          <t>G 组 马磊</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉（去年负责）</t>
+          <t>D 组 葛九明</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>晚宴席位/敬酒/现场对接</t>
+          <t>入场安检/可疑人员</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>F 组 彭常丽</t>
+          <t>G 组 康诺斯</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>B 组 王胜</t>
+          <t>G 组 刘严</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>交响乐团对接</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>F 组 朱俊峰</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（去年负责）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>晚宴席位/敬酒/现场对接</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>F 组 Winny</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>B 组 王胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>科创展位/赞助谈判</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>A 组 春子</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>议程脚本/会议记录/复盘</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>A 组 韦佳玉</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>无法解决/重大决策</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>韦佳玉 → 胡继刚</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1959,7 +2027,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>总策划缺席由韦佳玉全权代行</t>
+          <t>总策划缺席由韦佳玉全权代行；春子专注科创赞助</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2071,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>A 角 20 年策划经验+设备；B 角中信证券计时主控</t>
+          <t>A 角 20 年策划经验+自有设备；B 角中信证券计时主控</t>
         </is>
       </c>
     </row>
@@ -2037,17 +2105,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>张卓 盈科</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
           <t>随圣博</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>吕志翔</t>
-        </is>
-      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>B 角投融资人脉对接技术赞助方</t>
+          <t>A 角律师协调统筹；B 角技术执行（操作设备）</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2132,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>Winny 温妮</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>A 角建筑+协会运营；B 角对接赞助物料</t>
+          <t>A 角建筑+协会运营；B 角空窗期时间最多+零售运营</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2149,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>康诺斯</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>张卓</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>B 角律师可应对突发；蔡萍持急救证常驻医疗岗</t>
+          <t>A 角统筹机动调配；B 角持急救证常驻医疗岗★</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2239,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>副总策划，统筹各组</t>
+          <t>副总策划，统筹各组+文件总管</t>
         </is>
       </c>
     </row>
@@ -2229,17 +2297,17 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Winny 温妮</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>B 组 VIP</t>
+          <t>G 组组长</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>空窗期可承担时间敏感任务</t>
+          <t>应急安保+机动跨组调配</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2319,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>A 组秘书</t>
+          <t>A 组科创对接</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>科创资源对接（赞助/展位）</t>
+          <t>科创赞助/科技展位推进</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2388,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>总指挥</t>
+          <t>总指挥（胡继刚）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2334,12 +2402,12 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>执行调度</t>
+          <t>执行总监+文件总管（韦佳玉）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>对接 B/C/D/E/F/G 六组；时间节点把控；对讲机调度中枢</t>
+          <t>对接 B/C/D/E/F/G 六组；议程脚本/会议记录/复盘主持；对讲机调度中枢</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr"/>
@@ -2348,12 +2416,12 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>文件秘书</t>
+          <t>科创资源对接专员（春子）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>议程手册、签到表、嘉宾名单、流程脚本、复盘记录</t>
+          <t>聚焦科创赞助谈判+科技展位推进（自己提的科技展示建议自己主推）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
@@ -4916,7 +4984,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>全场最高决策，对接主办方与赞助方（腾讯/华为）</t>
+          <t>全场最高决策；对接主办方与赞助方（腾讯/华为）；与春子私下推进科技展位</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4996,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>执行总监/副总策划</t>
+          <t>执行总监/副总策划+文件总管</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -4948,7 +5016,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>总策划会上直接点名协助统筹；多届经验+资源整合</t>
+          <t>扩职：原李振春的文件秘书并入；统筹议程脚本/会议记录/各组协调/复盘主持</t>
         </is>
       </c>
     </row>
@@ -4960,7 +5028,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>文件秘书/科创联络</t>
+          <t>科创资源对接专员</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4980,7 +5048,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>主动承担+科创资源（可对接科技展示赞助）</t>
+          <t>★职责再细分：聚焦科创赞助谈判+科技展位推进（自己提出的科技展示建议由他与总策划主推）</t>
         </is>
       </c>
     </row>
@@ -5007,12 +5075,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>第三次参加最资深；原 F 副组长升任 B 组长</t>
+          <t>第三次参加最资深</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>总策划指定升任：第三次参加经验最足，接替蒋珊带 B 组</t>
+          <t>总策划指定升任：第三次参加经验最足，带 B 组</t>
         </is>
       </c>
     </row>
@@ -5088,27 +5156,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>VIP 1V1（核心搭子）</t>
+          <t>观众席引导</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Winny</t>
+          <t>Angi 郭杰</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>B/C/F均可 → B</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>空窗期时间最充裕、IP授权运营</t>
+          <t>国际贸易、首次</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>时间最充裕可全程紧贴VIP；总策划核心搭子之一</t>
+          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5188,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>观众席引导</t>
+          <t>动线引导</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Angi 郭杰</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -5135,44 +5203,44 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>国际贸易、首次</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
+          <t>标准引导岗</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>动线引导</t>
+          <t>组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、核心搭子</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>标准引导岗</t>
+          <t>总策划指定升任：20年策划经验+自有设备，全场制作把关</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5252,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>组长 / 舞台+设备总管</t>
+          <t>副组长 / 计时员</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -5199,12 +5267,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、核心搭子</t>
+          <t>中信证券，自报会务+倒计时</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>总策划指定升任：20年策划经验+自有设备，全场制作把关</t>
+          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
         </is>
       </c>
     </row>
@@ -5216,27 +5284,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 计时员</t>
+          <t>主持对接/串场</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C/B → C</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>中信证券，自报会务+倒计时</t>
+          <t>私募→律师、时间灵活、沟通强</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
+          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
         </is>
       </c>
     </row>
@@ -5248,27 +5316,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>主持对接/串场</t>
+          <t>PPT/资料对接</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>C/B → C</t>
+          <t>B/C → C</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>私募→律师、时间灵活、沟通强</t>
+          <t>建筑设计+地产+养老研究、首次</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
+          <t>细致岗，提前 24h 收齐讲者 PPT</t>
         </is>
       </c>
     </row>
@@ -5280,27 +5348,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>B/C → C</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>建筑设计+地产+养老研究、首次</t>
+          <t>一二级创投、K12教育</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>细致岗，提前 24h 收齐讲者 PPT</t>
+          <t>创投背景对接颁奖机构得体</t>
         </is>
       </c>
     </row>
@@ -5312,27 +5380,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行/机构对接</t>
+          <t>圆桌/机构嘉宾对接（调入）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B→E→C</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>一二级创投、K12教育</t>
+          <t>12级、投融资、教育/医疗/AI</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>创投背景对接颁奖机构得体</t>
+          <t>投融资人脉，对接 4 位圆桌嘉宾+主旨讲者上下场（技术非其专长，回归会务）</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5476,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AI 内容/新媒体（调入）</t>
+          <t>AI 内容/新媒体</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -5428,7 +5496,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>AI 圈层资源最强；从 B 组调入做新媒体（金句卡/朋友圈/小红书）</t>
+          <t>AI 圈层资源最强；新媒体（金句卡/朋友圈/小红书）</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5508,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>直播+交响乐预热</t>
+          <t>直播+交响乐预热+媒体接待</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -5460,39 +5528,39 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>主管直播；交响乐往届视频 T-7 起视频号每日预热</t>
+          <t>扩职：原马磊的媒体接待并入；主管直播+交响乐往届视频 T-7 起视频号每日预热</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>媒体接待+会后传播</t>
+          <t>组长 / 协调统筹（调入）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B/G → E</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>AI Club 生态、跨界资源</t>
+          <t>财税律师、二次参加、协调能力强</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>跨界资源+AI 圈层人脉，对接财经/科技媒体</t>
+          <t>总策划指定：律师协调能力强，统筹 E 组与场馆 AV 外包/陈潇工厂设备</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5572,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>组长 / 技术对接</t>
+          <t>副组长 / 技术执行</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -5524,7 +5592,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>唯一勾选 E，对接场馆 AV 外包+陈潇张江工厂设备</t>
+          <t>技术执行核心，对接场馆 AV 现场操作</t>
         </is>
       </c>
     </row>
@@ -5536,59 +5604,59 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>技术赞助/资源对接（调入）</t>
+          <t>技术对接助理</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>B → E</t>
+          <t>B → E（听安排）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>12级、投融资、教育/医疗/AI</t>
+          <t>同浦汇、首次</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>投融资人脉，对接腾讯/华为技术方+协调技术赞助资源</t>
+          <t>标准化对接执行</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>E</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>技术对接助理（调入）</t>
+          <t>组长 / 场地+物料+赞助物料</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>高辰辰</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>B → E（听安排）</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>同浦汇、首次</t>
+          <t>19级、建筑+市场开发、复旦网球协会运营</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>明确说听安排；从 B 调入做技术执行助理（标准化对接）</t>
+          <t>扩职：原刘严的赞助物料对接并入；建筑+协会运营经验主导场地与物料</t>
         </is>
       </c>
     </row>
@@ -5600,27 +5668,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>组长 / 场地+物料</t>
+          <t>副组长 / 茶歇+晚宴主管（调入）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>朱俊峰</t>
+          <t>Winny 温妮</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B/C/F均可 → F</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>19级、建筑+市场开发、复旦网球协会运营</t>
+          <t>空窗期时间最充裕、IP授权+MINISO运营</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>建筑专业+协会长期运营，最熟物料/场地落地</t>
+          <t>★最适合茶歇/晚宴：空窗期时间最多+零售运营+商务接待经验；从 B 调入做副组长</t>
         </is>
       </c>
     </row>
@@ -5632,59 +5700,59 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 物料+伴手礼+赞助物料</t>
+          <t>茶歇+晚宴专员</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>彭常丽</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>B/F → F</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>金融、二次参与</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>去年已熟悉流程，副手 Winny 主管 500 人茶歇+晚宴对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>组长 / 安保+机动调配（调入）</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
           <t>刘严</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>自报到F、平日接活多</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>F 组组员升副组长；专项对接腾讯/华为赞助物料入场（去年痛点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>茶歇+晚宴专员（调入）</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>彭常丽</t>
-        </is>
-      </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>B/F → F</t>
+          <t>F → G</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>金融、二次参与</t>
+          <t>自报积极、平日接活多、协调力强</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>去年已熟悉流程，从 B 调入主管 500 人茶歇+晚宴对接</t>
+          <t>总策划指定：从 F 副组长调任 G 组长，统筹安保+机动跨组调配</t>
         </is>
       </c>
     </row>
@@ -5696,12 +5764,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>组长 / 安保+机动调配</t>
+          <t>副组长 / 急救+医疗主岗 ★</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>康诺斯 Conns</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -5711,12 +5779,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>设计改造+碳资产、首次</t>
+          <t>复旦经院培训负责人(退休)、★持有急救证</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>做机动组长可跨组顶人</t>
+          <t>升任副组长；保留急救/医疗专项岗（持证稀缺技能）</t>
         </is>
       </c>
     </row>
@@ -5728,27 +5796,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 法务+舆情口径</t>
+          <t>机动 / 媒体应急口径（调入）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>B/G → G</t>
+          <t>D → G</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>财税律师、二次参加</t>
+          <t>AI Club 生态、跨界资源</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>律师处理舆情口径与突发法务最稳</t>
+          <t>媒体应急口径+跨界资源；G 组机动支援</t>
         </is>
       </c>
     </row>
@@ -5760,12 +5828,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>急救/医疗主岗 ★</t>
+          <t>机动 / 安保</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>康诺斯 Conns</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -5775,12 +5843,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>复旦经院培训负责人(退休)、★持有急救证</t>
+          <t>设计改造+碳资产、首次</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>★稀缺技能：自报有急救证；G 组急救/医疗专项岗</t>
+          <t>保留 G 组（自选偏好），机动支援+入场安检</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5943,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A - 执行总监/副总策划</t>
+          <t>A - 执行总监/副总策划+文件总管</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5892,7 +5960,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A - 文件秘书/科创联络</t>
+          <t>A - 科创资源对接专员</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -5960,12 +6028,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B - VIP 1V1（核心搭子）</t>
+          <t>B - 观众席引导</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Winny</t>
+          <t>Angi 郭杰</t>
         </is>
       </c>
       <c r="C10" s="5" t="n"/>
@@ -5977,12 +6045,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B - 观众席引导</t>
+          <t>B - 动线引导</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Angi 郭杰</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -5994,12 +6062,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>B - 动线引导</t>
+          <t>C - 组长 / 舞台+设备总管</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -6011,12 +6079,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C - 组长 / 舞台+设备总管</t>
+          <t>C - 副组长 / 计时员</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -6028,12 +6096,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C - 副组长 / 计时员</t>
+          <t>C - 主持对接/串场</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -6045,12 +6113,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C - 主持对接/串场</t>
+          <t>C - PPT/资料对接</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -6062,12 +6130,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C - PPT/资料对接</t>
+          <t>C - 颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -6079,12 +6147,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C - 颁奖执行/机构对接</t>
+          <t>C - 圆桌/机构嘉宾对接（调入）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -6130,7 +6198,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>D - AI 内容/新媒体（调入）</t>
+          <t>D - AI 内容/新媒体</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -6147,7 +6215,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>D - 直播+交响乐预热</t>
+          <t>D - 直播+交响乐预热+媒体接待</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -6164,12 +6232,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>D - 媒体接待+会后传播</t>
+          <t>E - 组长 / 协调统筹（调入）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -6181,7 +6249,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>E - 组长 / 技术对接</t>
+          <t>E - 副组长 / 技术执行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -6198,12 +6266,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>E - 技术赞助/资源对接（调入）</t>
+          <t>E - 技术对接助理</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>高辰辰</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -6215,12 +6283,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>E - 技术对接助理（调入）</t>
+          <t>F - 组长 / 场地+物料+赞助物料</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>高辰辰</t>
+          <t>朱俊峰</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -6232,12 +6300,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>F - 组长 / 场地+物料</t>
+          <t>F - 副组长 / 茶歇+晚宴主管（调入）</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>朱俊峰</t>
+          <t>Winny 温妮</t>
         </is>
       </c>
       <c r="C26" s="5" t="n"/>
@@ -6249,12 +6317,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>F - 副组长 / 物料+伴手礼+赞助物料</t>
+          <t>F - 茶歇+晚宴专员</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>彭常丽</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -6266,12 +6334,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>F - 茶歇+晚宴专员（调入）</t>
+          <t>G - 组长 / 安保+机动调配（调入）</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>彭常丽</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -6283,12 +6351,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>G - 组长 / 安保+机动调配</t>
+          <t>G - 副组长 / 急救+医疗主岗 ★</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>康诺斯 Conns</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -6300,12 +6368,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>G - 副组长 / 法务+舆情口径</t>
+          <t>G - 机动 / 媒体应急口径（调入）</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -6317,12 +6385,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>G - 急救/医疗主岗 ★</t>
+          <t>G - 机动 / 安保</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>康诺斯 Conns</t>
         </is>
       </c>
       <c r="C31" s="5" t="n"/>

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -1475,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1908,7 +1908,7 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>科创展位/赞助谈判</t>
+          <t>嘉宾邀约确认/全程跟进</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1918,39 +1918,56 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>韦佳玉 → 胡继刚</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>议程脚本/会议记录/复盘</t>
+          <t>赞助资源/物料落位</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>A 组 韦佳玉</t>
+          <t>A 组 春子</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>F 组 朱俊峰 → 胡继刚</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>议程脚本/会议记录/复盘</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>A 组 韦佳玉</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>无法解决/重大决策</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>韦佳玉 → 胡继刚</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2027,7 +2044,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>总策划缺席由韦佳玉全权代行；春子专注科创赞助</t>
+          <t>总策划缺席由韦佳玉全权代行；春子专注嘉宾邀约+赞助资源落位</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2336,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>A 组科创对接</t>
+          <t>A 组嘉宾+赞助落位</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>科创赞助/科技展位推进</t>
+          <t>嘉宾邀约确认/跟进 + 赞助资源对接落位</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2433,12 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>科创资源对接专员（春子）</t>
+          <t>嘉宾邀约+赞助落位（春子）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>聚焦科创赞助谈判+科技展位推进（自己提的科技展示建议自己主推）</t>
+          <t>①嘉宾邀约确认与全程跟进（外地交通/住宿）  ②赞助资源对接落位（腾讯/华为/科技展位）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
@@ -5028,7 +5045,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>科创资源对接专员</t>
+          <t>嘉宾邀约+赞助资源落位</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5048,7 +5065,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>★职责再细分：聚焦科创赞助谈判+科技展位推进（自己提出的科技展示建议由他与总策划主推）</t>
+          <t>★职责聚焦：①嘉宾邀约确认与全程跟进（含外地嘉宾交通/住宿）②赞助资源对接落位（腾讯/华为/科技展位）</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5977,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A - 科创资源对接专员</t>
+          <t>A - 嘉宾邀约+赞助资源落位</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -6610,9 +6627,9 @@
           <t>增加科技类展示（AI/机器人/芯片小海报）</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>暂缓→单列待办</t>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -6622,7 +6639,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>需赞助谈判，春子+胡继刚 私下推进，不进 5/22 必交付</t>
+          <t>★春子已任 A 组嘉宾邀约+赞助资源落位专员；该建议作为其 KPI 之一推进</t>
         </is>
       </c>
     </row>

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -20,7 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11-嘉宾时间控制SOP" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-对接联系人清单" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-组长AB角备份" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-核心策划圈" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-当日到场时间" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-核心策划圈" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,7 +79,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +126,11 @@
         <fgColor rgb="00808080"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE4B0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -152,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -187,6 +193,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -873,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -959,17 +968,17 @@
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>T-7 (5/15)</t>
+          <t>T-8 (5/14)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>晚宴名单锁定 V1（去年痛点：太晚锁定）</t>
+          <t>★ 各组组长整理本组任务清单 V1（按议程节点拆解+按时间排期）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>B+F</t>
+          <t>各组组长</t>
         </is>
       </c>
     </row>
@@ -981,12 +990,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>交响乐往届视频开始日更预热（视频号）</t>
+          <t>★ 各组任务清单 V1 汇总到 A 组+总策划评审</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+各组长</t>
         </is>
       </c>
     </row>
@@ -998,92 +1007,92 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>现场踏勘 1（场地/动线/AV）</t>
+          <t>晚宴名单锁定 V1（去年痛点：太晚锁定）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A+C+E+F</t>
+          <t>B+F+春子</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>所有讲者 PPT 截稿（去年是 T-3，今年提前）</t>
+          <t>嘉宾邀约确认 V1（春子专项 KPI）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>春子</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>地铁→场地快进短视频拍摄完成</t>
+          <t>交响乐往届视频开始日更预热（视频号）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>D+F</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>物料/胸牌印刷下单（去年痛点：名牌制作晚）</t>
+          <t>现场踏勘 1（场地/动线/AV）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A+C+E+F</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>T-4 (5/18)</t>
+          <t>T-6 (5/16)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>腾讯/华为赞助物料对接清单确认</t>
+          <t>★ 各组任务清单 V2（含问题修正）下发到组员</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>F+A</t>
+          <t>各组组长</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
+          <t>所有讲者 PPT 截稿（去年是 T-3，今年提前）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1095,168 +1104,321 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
+          <t>地铁→场地快进短视频拍摄完成</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D+F</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>短视频发主群+嘉宾群预热</t>
+          <t>物料/胸牌印刷下单（去年痛点：名牌制作晚）</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-4 (5/18)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
+          <t>腾讯/华为赞助物料对接清单确认（春子主推）</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>春子+F</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>现场踏勘 2（含彩排站位）</t>
+          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>A+C+E</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>全员线上彩排 18:00-19:30（1.5h）</t>
+          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>A+全员</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>全设备压力测试+陈潇工厂设备进场</t>
+          <t>短视频发主群+嘉宾群预热</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>T-0 09:00</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>现场指挥部成立、对讲机分发、AED/急救包就位</t>
+          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>A+G</t>
+          <t>B+春子</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>T-0 12:00</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>签到台开台、VIP 车队首班、直播试推流</t>
+          <t>现场踏勘 2（含彩排站位）</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>B+D</t>
+          <t>A+C+E</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>T-0 13:25</t>
+          <t>T-1 (5/21)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>全员就位静默 5 分钟、广播开场倒计时</t>
+          <t>全员线上彩排 18:00-19:30（1.5h）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+全员</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>全设备压力测试+陈潇工厂设备进场</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>T-0 09:00</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>★ A/F/G 三组到场：指挥部+物料布置+AED急救包就位</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>A+F+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>T-0 10:00</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>★ C 会务+E 技术到场：走台彩排+设备联调</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:00</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体到场：机位调试+直播试推流</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:30</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>B 接待到场：签到台开台+VIP陪同上岗</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>T-0 12:00</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>全员就位；VIP 车队首班；签到 13:00 开放</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>T-0 13:25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>全员静默 5 分钟、广播开场倒计时</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>T-0 15:00</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>★ 晚宴专项人员到场：F/B/D/G 晚宴组分批进入晚宴厅</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>F+B+D+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>T-0 18:30</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>晚宴开席</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>T+1</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>通稿次日 10:00 前发布、复盘会、问题归档</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>A+D</t>
         </is>
@@ -1988,7 +2150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2029,7 +2191,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>A 统筹</t>
+          <t>总指挥</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -2039,142 +2201,164 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>韦佳玉 / 陈潇</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>总策划缺席由韦佳玉全权代行；春子专注嘉宾邀约+赞助资源落位</t>
+          <t>★双执行总监：韦佳玉统筹方向 + 陈潇会务方向</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>B 接待</t>
+          <t>A 统筹</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>王胜</t>
+          <t>韦佳玉（执行总监①）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>朱铭喆</t>
+          <t>春子</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>A 角第三次参加最资深；B 角港校联络人</t>
+          <t>统筹方向；春子专注嘉宾邀约+赞助资源落位</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>C 会务</t>
+          <t>B 接待</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王胜</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>朱铭喆</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>A 角 20 年策划经验+自有设备；B 角中信证券计时主控</t>
+          <t>A 角第三次参加最资深；B 角港校联络人</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>D 媒体</t>
+          <t>C 会务</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>陈潇（执行总监②）</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>A 角总策划指定；B 角自媒体+摄影核心岗</t>
+          <t>★ 双执行总监会务方向；自有设备+20 年策划</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>E 技术</t>
+          <t>D 媒体</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>随圣博</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>A 角律师协调统筹；B 角技术执行（操作设备）</t>
+          <t>A 角总策划指定；B 角自媒体+摄影核心岗</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>F 后勤</t>
+          <t>E 技术</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>朱俊峰</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Winny 温妮</t>
+          <t>随圣博</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>A 角建筑+协会运营；B 角空窗期时间最多+零售运营</t>
+          <t>A 角律师协调统筹；B 角技术执行（操作设备）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>F 后勤</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Winny 温妮</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>A 角建筑+协会运营；B 角空窗期时间最多+零售运营</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
           <t>G 应急</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>刘严</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>蔡萍</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>A 角统筹机动调配；B 角持急救证常驻医疗岗★</t>
         </is>
@@ -2189,6 +2373,396 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>5/22 当日各组到场时间表（按总策划指令：会务 10:00 / 晚宴 15:00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>上午 09:00 A/F/G 三组；10:00 C/E；11:00 D；11:30 B；15:00 晚宴专项启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>到场时间</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>组 / 人员范围</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>到场人员</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>到场即开始做的事</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>A 统筹（全员）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚 / 韦佳玉 / 春子</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>现场指挥部建立 / 对讲机分发 / 与各组组长进度核对</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>F 后勤（全员）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰 / Winny / 彭常丽</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>场地桌椅布置 / 物料进场 / 茶歇位铺设 / 赞助物料对接（腾讯/华为）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>G 应急（全员）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>刘严 / 蔡萍 / 马磊 / 康诺斯</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>安检设备就位 / AED+急救包 3 处摆放 / 医疗对接热线打通 / 入场安检上岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>★ C 会务（全员）</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>陈潇 / 王珏 / 冯墨 / 黄璐 / 徐胜博 / 吕志翔</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>舞台走台彩排 / 计时器+举牌就位 / 嘉宾上下场动线对脚本 / PPT 顺序加载主机</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>★ E 技术（全员）</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>张卓 / 随圣博 / 高辰辰</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>音响 / 麦克风 / PPT 切换 / 灯光 / LED / 网络直播 全设备联调</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体（全员）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>葛九明 / 张蒙 / 蒋珊 / 皮尔德小号</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>摄影机位调试 / 直播试推流 / 签到合影区开放 / 媒体接待区铺设</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>B 接待（全员）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>王胜 / 朱铭喆 / JasonCAI / Angi / LV</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>签到台开台 / VIP 1V1 陪同上岗 / 引导动线就位 / 休息室检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>全员就位</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>全 27 人</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>午餐 12:30 前完成；VIP 车队首班；13:00 签到开放</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>全员静默</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>全 27 人</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>总策划广播开场倒计时；C 组主持人就位；E 组麦克风电池满电</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>★ 15:00</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>F 晚宴专项</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Winny（茶歇晚宴主管）+ 彭常丽</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>★ 晚宴餐厅最终对接 / 席位卡核对 / 敬酒流程预演 / 桌花布置</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>B 接待晚宴</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>王胜 + 朱铭喆 + JasonCAI</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>晚宴桌次引导脚本对接 / VIP 敬酒顺序确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体晚宴</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>皮尔德小号 + 张蒙</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>晚宴花絮拍摄准备 / 当晚短视频脚本</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>G 应急晚宴</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>康诺斯 + 马磊</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>晚宴入口二次核验 / 车队调度对接 / 离场分流预案</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>晚宴开席</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>陈潇司仪过场 / 总策划致辞 / Winny 主管节奏</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>撤场</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>F 组负责场地交还；G 组安全确认；A 组复盘 30min</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2239,7 +2813,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>全场指挥</t>
+          <t>全场指挥；统筹两位执行总监</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2825,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>A 执行总监</t>
+          <t>★ 执行总监 ① 统筹方向</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>副总策划，统筹各组+文件总管</t>
+          <t>议程脚本/会议记录/各组协调/复盘主持</t>
         </is>
       </c>
     </row>
@@ -2268,80 +2842,80 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>C 组组长</t>
+          <t>★ 执行总监 ② 会务方向</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>提供灯光/舞台/音响设备资源</t>
+          <t>C 组组长；流程/舞台/设备/制作（自有灯光音响）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>王胜</t>
+          <t>李振春 春子</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>B 组组长</t>
+          <t>嘉宾邀约+赞助落位</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>三次参加，老带新</t>
+          <t>①嘉宾邀约确认与跟进 ②赞助资源对接落位</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>王胜</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>D 组组长</t>
+          <t>B 组组长</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>总策划指定，统筹媒体宣传</t>
+          <t>三次参加，老带新；嘉宾接待主管</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>G 组组长</t>
+          <t>D 组组长</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>应急安保+机动跨组调配</t>
+          <t>总策划指定，统筹媒体宣传</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>李振春 春子</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>A 组嘉宾+赞助落位</t>
+          <t>G 组组长</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>嘉宾邀约确认/跟进 + 赞助资源对接落位</t>
+          <t>应急安保+机动跨组调配</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2410,7 +2984,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>全场最高决策；与主办/协办方对接；流程总控</t>
+          <t>全场最高决策；与主办/协办方对接；统筹双执行总监</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
@@ -2419,12 +2993,12 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>执行总监+文件总管（韦佳玉）</t>
+          <t>执行总监① 统筹方向（韦佳玉）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>对接 B/C/D/E/F/G 六组；议程脚本/会议记录/复盘主持；对讲机调度中枢</t>
+          <t>议程脚本/会议记录/各组协调/复盘主持；对讲机调度中枢</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr"/>
@@ -2433,44 +3007,44 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>执行总监② 会务方向（陈潇 Kelly）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>流程/舞台/设备/制作（兼 C 组组长）；与韦佳玉并列</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>嘉宾邀约+赞助落位（春子）</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>①嘉宾邀约确认与全程跟进（外地交通/住宿）  ②赞助资源对接落位（腾讯/华为/科技展位）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>①嘉宾邀约确认与全程跟进（外地交通/住宿） ②赞助资源对接落位</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>B 嘉宾接待组</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>VIP一对一</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>为主旨演讲嘉宾/主持/特邀机构嘉宾配备 1V1 陪同（白硕、夏春、寇文红等）</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>机场/酒店接送</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>外地嘉宾接机/接站、酒店入住对接、当日接送车辆调度</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
@@ -2479,12 +3053,12 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>签到台</t>
+          <t>机场/酒店接送</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>按嘉宾分级（VVIP / 演讲嘉宾 / 机构嘉宾 / 普通嘉宾）分通道签到</t>
+          <t>外地嘉宾接机/接站、酒店入住对接、当日接送车辆调度</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr"/>
@@ -2493,12 +3067,12 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>引导动线</t>
+          <t>签到台</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>电梯口→签到台→主会场→洗手间→茶歇区→晚宴厅 全程引导</t>
+          <t>按嘉宾分级（VVIP / 演讲嘉宾 / 机构嘉宾 / 普通嘉宾）分通道签到</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
@@ -2507,12 +3081,12 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>休息室管理</t>
+          <t>引导动线</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>嘉宾休息室饮水、补妆、PPT预演、专属服务</t>
+          <t>电梯口→签到台→主会场→洗手间→茶歇区→晚宴厅 全程引导</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
@@ -2521,44 +3095,44 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>休息室管理</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>嘉宾休息室饮水、补妆、PPT预演、专属服务</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>名片/合影</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>重要嘉宾合影、名片收集、对接需求登记</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>C 会务执行组</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>流程总控</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>持脚本对照议程；每环节超时 30s 即时提醒主持/总指挥</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>舞台引导</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>嘉宾候场→上台→落座→下场；圆桌座次摆名牌</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr"/>
@@ -2567,12 +3141,12 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>计时员</t>
+          <t>舞台引导</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>主旨 25/20min、圆桌 40min；倒计时举牌（5/3/1 min）</t>
+          <t>嘉宾候场→上台→落座→下场；圆桌座次摆名牌</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
@@ -2581,12 +3155,12 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>主持对接</t>
+          <t>计时员</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>提前与各环节主持人对脚本；过场词、串场调整</t>
+          <t>主旨 25/20min、圆桌 40min；倒计时举牌（5/3/1 min）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr"/>
@@ -2595,12 +3169,12 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>主持对接</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>提前 24h 收齐所有讲者 PPT；按演讲顺序入备份U盘+云盘</t>
+          <t>提前与各环节主持人对脚本；过场词、串场调整</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
@@ -2609,44 +3183,44 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>PPT/资料对接</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>提前 24h 收齐所有讲者 PPT；按演讲顺序入备份U盘+云盘</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>颁奖执行</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>奖杯/证书摆放、颁奖嘉宾引导、获奖机构合影</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>D 媒体宣传组</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>摄影/摄像</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>主舞台机位+游机；圆桌特写；签到/茶歇/晚宴花絮</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>直播/录播</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>直播平台搭建（如视频号/抖音）；导播切换；网络备用 4G</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
@@ -2655,12 +3229,12 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>媒体接待</t>
+          <t>直播/录播</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>财经/科技媒体记者签到、采访区安排、通稿派发</t>
+          <t>直播平台搭建（如视频号/抖音）；导播切换；网络备用 4G</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
@@ -2669,12 +3243,12 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>新媒体即时发布</t>
+          <t>媒体接待</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>现场快讯（金句卡片）、嘉宾观点摘录、朋友圈/小红书推送</t>
+          <t>财经/科技媒体记者签到、采访区安排、通稿派发</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
@@ -2683,44 +3257,44 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
+          <t>新媒体即时发布</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>现场快讯（金句卡片）、嘉宾观点摘录、朋友圈/小红书推送</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>会后传播</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>活动通稿、视频剪辑、嘉宾合影分发、媒体追投</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>E 技术支持组</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>音响/麦克风</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>手持/领夹麦各 4 支；圆桌每位 1 支；备用电池常驻</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>PPT切换/总控</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>翻页器+技术员守机；嘉宾切换提前 1 环节预加载</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
@@ -2729,12 +3303,12 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>灯光</t>
+          <t>PPT切换/总控</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>舞台主光、圆桌追光、交响乐演出灯光预案</t>
+          <t>翻页器+技术员守机；嘉宾切换提前 1 环节预加载</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
@@ -2743,12 +3317,12 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>LED大屏/字幕</t>
+          <t>灯光</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>主屏播放+侧屏倒计时/嘉宾介绍卡</t>
+          <t>舞台主光、圆桌追光、交响乐演出灯光预案</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
@@ -2757,12 +3331,12 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>网络/直播</t>
+          <t>LED大屏/字幕</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>主有线+4G双备份；直播推流监看；断网应急脚本</t>
+          <t>主屏播放+侧屏倒计时/嘉宾介绍卡</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
@@ -2771,44 +3345,44 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="inlineStr">
         <is>
+          <t>网络/直播</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>主有线+4G双备份；直播推流监看；断网应急脚本</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>应急备件</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>备用麦×2、备用电脑×1、备用翻页器×2、转接头全套</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>F 后勤保障组</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>场地/桌椅</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>主会场布置、圆桌摆位、签到台、媒体区、休息室</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>物料制作</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>议程册、桌牌、横幅、KT板、引导牌、嘉宾胸卡</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr"/>
@@ -2817,12 +3391,12 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>茶歇/饮水</t>
+          <t>物料制作</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>全程饮水补给；15:45音乐会期间高端茶歇（500人量）</t>
+          <t>议程册、桌牌、横幅、KT板、引导牌、嘉宾胸卡</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr"/>
@@ -2831,12 +3405,12 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>伴手礼</t>
+          <t>茶歇/饮水</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>按等级（VVIP/嘉宾/机构）分类分发，签到台同步领取</t>
+          <t>全程饮水补给；15:45音乐会期间高端茶歇（500人量）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr"/>
@@ -2845,12 +3419,12 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>交响乐团对接</t>
+          <t>伴手礼</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>陆家嘉交响乐团到场、化妆间、乐器、调音、彩排时间</t>
+          <t>按等级（VVIP/嘉宾/机构）分类分发，签到台同步领取</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr"/>
@@ -2859,44 +3433,44 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>交响乐团对接</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>陆家嘉交响乐团到场、化妆间、乐器、调音、彩排时间</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
           <t>VIP晚宴</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>席位卡、菜单、酒水、桌花、敬酒流程、餐厅对接</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>G 应急安全/机动组</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>入场安检</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>胸卡核验、闲杂人员拒入、可疑物品筛查</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>现场巡视</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>通道畅通、消防通道无堵塞、舞台周边安全</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr"/>
@@ -2905,12 +3479,12 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>医疗急救</t>
+          <t>现场巡视</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>AED 位置已知、急救包、最近医院路线（含车辆待命）</t>
+          <t>通道畅通、消防通道无堵塞、舞台周边安全</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
@@ -2919,12 +3493,12 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>舆情/口径</t>
+          <t>医疗急救</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>突发负面言论时的回应口径；与 D 组联动撤稿/澄清</t>
+          <t>AED 位置已知、急救包、最近医院路线（含车辆待命）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr"/>
@@ -2933,26 +3507,40 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
+          <t>舆情/口径</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>突发负面言论时的回应口径；与 D 组联动撤稿/澄清</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>VIP/晚宴安保</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>晚宴 500 人圈层活动安全；车队动线；离场分流</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A8:A13"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A37:A41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5001,7 +5589,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>全场最高决策；对接主办方与赞助方（腾讯/华为）；与春子私下推进科技展位</t>
+          <t>全场最高决策；对接主办方与赞助方（腾讯/华为）；统筹两位执行总监</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5601,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>执行总监/副总策划+文件总管</t>
+          <t>执行总监 ① 统筹方向</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -5033,7 +5621,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>扩职：原李振春的文件秘书并入；统筹议程脚本/会议记录/各组协调/复盘主持</t>
+          <t>分管统筹：议程脚本/会议记录/各组协调/复盘主持；与陈潇双执行总监并列</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5825,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>组长 / 舞台+设备总管</t>
+          <t>★ 执行总监 ② 会务方向 / C 组组长</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5257,7 +5845,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>总策划指定升任：20年策划经验+自有设备，全场制作把关</t>
+          <t>总策划设立双执行总监：陈潇分管会务执行方向（流程/舞台/设备/制作）；与韦佳玉并列向总策划负责</t>
         </is>
       </c>
     </row>
@@ -5960,7 +6548,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A - 执行总监/副总策划+文件总管</t>
+          <t>A - 执行总监 ① 统筹方向</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -6079,7 +6667,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C - 组长 / 舞台+设备总管</t>
+          <t>C - ★ 执行总监 ② 会务方向 / C 组组长</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -20,8 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11-嘉宾时间控制SOP" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12-对接联系人清单" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13-组长AB角备份" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-当日到场时间" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-核心策划圈" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14a-外部对接人" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14b-外部沟通群" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14c-晚宴流程" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-当日到场时间" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-核心策划圈" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -882,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1070,97 +1073,97 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>T-6 (5/16)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>★ 各组任务清单 V2（含问题修正）下发到组员</t>
+          <t>★ 茶歇盒马群拉群打招呼（林爱平）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>各组组长</t>
+          <t>F 朱俊峰</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>所有讲者 PPT 截稿（去年是 T-3，今年提前）</t>
+          <t>★ 一滴水场地沟通群拉群（含洋洋得意/吴伟）</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>胡继刚</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>地铁→场地快进短视频拍摄完成</t>
+          <t>★ PPT 沟通群拉群（讲者+C+E+陈潇）</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>D+F</t>
+          <t>C 陈潇</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>T-5 (5/17)</t>
+          <t>T-7 (5/15)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>物料/胸牌印刷下单（去年痛点：名牌制作晚）</t>
+          <t>★ 伴手礼/赞助沟通群拉群</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>胡继刚+春子</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>T-4 (5/18)</t>
+          <t>T-6 (5/16)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>腾讯/华为赞助物料对接清单确认（春子主推）</t>
+          <t>★ 组长会议（已完成）→ 同步纪要 + 各组任务 V2 下发</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>春子+F</t>
+          <t>各组组长+韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
+          <t>所有讲者 PPT 截稿（去年是 T-3，今年提前）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1172,253 +1175,474 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
+          <t>地铁→场地快进短视频拍摄完成</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D+F</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>T-3 (5/19)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>短视频发主群+嘉宾群预热</t>
+          <t>★ 班尼杨对接：手环 4 种+论坛道具+晚宴大屏模板</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C 陈潇+E 张卓</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
+          <t>★ 刘总赞助酒水/饮料发货（异地 2-3 天物流）</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>B+春子</t>
+          <t>F 刘严</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-5 (5/17)</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>现场踏勘 2（含彩排站位）</t>
+          <t>物料/胸牌印刷下单</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>A+C+E</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-4 (5/18)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>全员线上彩排 18:00-19:30（1.5h）</t>
+          <t>腾讯/华为/蔚来赞助物料对接清单确认（春子主推）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>A+全员</t>
+          <t>春子+F</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>全设备压力测试+陈潇工厂设备进场</t>
+          <t>★ 晚宴抽奖奖品确认（一/二/三等奖）</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>韦佳玉+赞助</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>T-0 09:00</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>★ A/F/G 三组到场：指挥部+物料布置+AED急救包就位</t>
+          <t>★ 节目供应商提案确认（陈潇推荐）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>A+F+G</t>
+          <t>陈潇+韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>T-0 10:00</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>★ C 会务+E 技术到场：走台彩排+设备联调</t>
+          <t>★ 前两排观众+发奖人提前通知文档化</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>C 徐胜博</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>T-0 11:00</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>D 媒体到场：机位调试+直播试推流</t>
+          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>T-0 11:30</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>B 接待到场：签到台开台+VIP陪同上岗</t>
+          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>T-0 12:00</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>全员就位；VIP 车队首班；签到 13:00 开放</t>
+          <t>短视频发主群+嘉宾群预热</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>全员</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>T-0 13:25</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>全员静默 5 分钟、广播开场倒计时</t>
+          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+春子</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>T-0 15:00</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>★ 晚宴专项人员到场：F/B/D/G 晚宴组分批进入晚宴厅</t>
+          <t>现场踏勘 2（含彩排站位）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>F+B+D+G</t>
+          <t>A+C+E</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>T-0 18:30</t>
+          <t>T-1 (5/21) 下午</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>晚宴开席</t>
+          <t>★ 现场踏勘 2 + 吴伟灯光位置确认 + 讲台尺寸量取</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>全员</t>
+          <t>A+C+E+F+佳玉</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>全员线上彩排 18:00-19:30（1.5h）</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>A+全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>★ 主讲台胸花+讲台花到货（按尺寸定制）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>F+王胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>★ 伴手礼到货+统一分装到袋（1-2 小时）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>F+其他组支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>T-1 (5/21)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>全设备压力测试+陈潇工厂设备进场（如需）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>T-0 08:30</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>★ 会务公司班尼杨设备入场（不需提前一天）</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>E+班尼杨</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>T-0 09:00</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>★ A/F/G 三组到场：指挥部+物料布置+AED急救包就位</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>A+F+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>T-0 10:00</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>★ C 会务+E 技术到场：走台彩排+设备联调</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:00</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体到场：机位调试+直播试推流</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:30</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>B 接待到场：签到台开台+VIP陪同上岗</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>T-0 12:00</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>全员就位；VIP 车队首班；签到 13:00 开放</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>T-0 13:25</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>全员静默 5 分钟、广播开场倒计时</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>T-0 15:00</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>★ 晚宴专项人员到场：F/B/D/G 晚宴组分批进入晚宴厅</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>F+B+D+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>T-0 18:30</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>晚宴开席</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>T+1</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>通稿次日 10:00 前发布、复盘会、问题归档</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>A+D</t>
         </is>
@@ -1637,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2132,6 +2356,125 @@
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>会务公司（舞台/道具/音响）</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>班尼杨 312（C 陈潇主对接）</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>E 张卓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>白天主持人/串场对接</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>米兰达（吕苗苗）→ 陈潇</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>场地/停车/讲台尺寸/胸花尺寸</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>洋洋得意（一滴水物业）</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>F 朱俊峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>茶歇（盒马）</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>林爱平（F 朱俊峰拉群）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>彭常丽</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>一滴水灯光</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>吴伟（E 张卓 21 号下午对接）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>随圣博</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>赞助酒水/饮料（异地发货）</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>刘总（F 刘严对接）</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>春子</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>晚宴 PM</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（兼任）</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>陈潇</t>
         </is>
       </c>
     </row>
@@ -2378,6 +2721,716 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>外部对接人清单（5/16 组长会议落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>重点：避免大家单独加场地/会务方；统一通过这些联系人对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>姓名 / 标识</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>联系方式</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>主要对接事项</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>责任组</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>会务公司</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>班尼杨（昵称班尼y，微信号 312）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>微信 312</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>舞台搭建 / 论坛道具 / 倒计时牌 / 音响 / 电脑 3-4 台 / 标识手环</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>C 陈潇 + E 张卓</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>白天主持人</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>米兰达（吕苗苗）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>微信群内</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>主持稿（需提供：议程+赞助方+主办协办+合影时间）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>C 陈潇</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>晚宴主持人</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>（另定）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>晚宴串场+抽奖+敬酒环节</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>C 陈潇 + 韦佳玉（晚宴 PM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>场地方一滴水</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>洋洋得意（物业对接人）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>群名「洋洋得意」</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>停车 / 收费 / 货拉拉引导 / 桌椅 / 讲台尺寸 / 胸花尺寸 / KT板</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>F 朱俊峰 + B 王胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>一滴水灯光</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>吴伟</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>灯光调试+使用方法（21 号下午到场确认位置）</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>E 张卓 + 随圣博</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>茶歇供应商</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>林爱平（盒马）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>去年合作人，提前一周联系</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>茶歇采购 + 现切果盘（盒马自带装备）</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>F 朱俊峰 + 彭常丽</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>赞助酒水/饮料</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>刘总</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>异地发货（物流 2-3 天），收件人写胡继刚</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>F 刘严 + 春子</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>赞助方</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>腾讯 / 华为汽车 / 蔚来 / 银行 / 券商</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚直对</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>赞助物料 + 致辞嘉宾 + 伴手礼比例</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚 + 春子</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>外部沟通群清单（5/16 组长会议落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>原则：横向沟通最容易漏；用专项群替代单点对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>群名/用途</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>拉群责任人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>群内成员</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>年度峰会组长群</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚（已建）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>总策划+7 组长+韦佳玉+陈潇</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>横向沟通主阵地；班尼杨+米兰达+洋洋得意已拉入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>PPT 沟通群 / 搜 PPT 群</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>陈潇</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>C 组+E 组+所有讲者</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>PPT 收集+尺寸告知+反复版本跟进（去年痛点：尺寸不对调很久）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>伴手礼/赞助沟通群</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>F 组+所有赞助方+春子</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>伴手礼到货时间+份数（按赞助比例）+赞助物料协调</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>一滴水场地沟通群</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚（新拉）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>全员+洋洋得意+吴伟</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>★避免大家单独加物业；停车/桌椅/灯光/KT板/讲台尺寸统一沟通</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>茶歇盒马群</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>F 组 朱俊峰</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>F 组+林爱平</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>茶歇采购（提前一周建群打招呼）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>会务公司技术群</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>陈潇</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>C 组+E 组+班尼杨</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>舞台/音响/电脑/论坛道具/倒计时牌</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>晚宴流程（韦佳玉任晚宴 PM · 5/16 落地）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>晚宴在一楼大厅（去年三楼场地今年不可用）；曲面长 LED 屏播放 PPT 模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>环节</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>责任人</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>关键动作 / 物料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>嘉宾入场+引导</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>B 王胜+朱铭喆+JasonCAI</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>晚宴手环核验（与下午手环不同色）+席位引导</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>18:30-18:35</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>开席+晚宴主持人开场</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>晚宴主持人</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>陈潇司仪过场；曲面 LED 屏开场致辞 PPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>18:35-18:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>总策划致辞+开瓶敬酒</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>互动交杯环节；技术组放背景音乐</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>18:45-19:00</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>赞助商代表致辞</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>春子协调赞助方</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>腾讯/华为/蔚来/银行/券商代表（视赞助比例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>19:00-19:40</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>节目表演（节目供应商）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>陈潇 Kelly 推荐供应商</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>供应商提案；不搭台（用场地方现有台子）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>19:40-20:00</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>抽奖环节（一/二/三等奖）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉（晚宴 PM）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>奖品预算与赞助商对接；主持人念号</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>20:00-20:30</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>自由社交+合影+敬酒</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>D 组花絮拍摄；G 组维持秩序+车队待命</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>撤场</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>F+G</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>场地交还+车队调度+离场分流</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2762,7 +3815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4798,7 +5851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4855,7 +5908,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>600 份</t>
+          <t>800 份（按 500 准备，预留 300）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -4865,7 +5918,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>T-5 印刷完成（前移）</t>
+          <t>T-5 印刷完成</t>
         </is>
       </c>
     </row>
@@ -4877,22 +5930,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>桌牌/嘉宾胸卡</t>
+          <t>席卡（前 4 排 + 圆桌嘉宾）</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>全员</t>
+          <t>前 4 排 = 约 80 张 + 圆桌 12 张</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F+B</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>T-2 完成（去年痛点：太晚）</t>
+          <t>T-2 完成（按最终名单）</t>
         </is>
       </c>
     </row>
@@ -4904,12 +5957,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>★志愿者专用橙色胸牌</t>
+          <t>★ 嘉宾胸卡（仅工作人员+演讲嘉宾）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>26 张（含韦佳玉）</t>
+          <t>约 50 张（500人不发，去年经验）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -4919,7 +5972,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>T-2 完成（采纳张蒙建议）</t>
+          <t>T-2</t>
         </is>
       </c>
     </row>
@@ -4931,22 +5984,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>签到表/电子签到</t>
+          <t>★ 入场标识 4 种手环 / 贴纸</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>分级 4 类</t>
+          <t>下午嘉宾 + 下午工作人员 + 晚宴嘉宾 + 晚宴工作人员</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>F+B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>当日 12:00 上线</t>
+          <t>T-2 找会务公司班尼杨制作（替代 500 人胸牌方案）</t>
         </is>
       </c>
     </row>
@@ -4958,12 +6011,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>横幅/KT板/引导牌</t>
+          <t>★ 志愿者专用橙色胸牌</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>全场</t>
+          <t>27 张（含韦佳玉）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -4973,115 +6026,115 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>当日 10:00 前</t>
+          <t>T-2 完成（张蒙建议）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>手持麦×4 / 领夹麦×4</t>
+          <t>横幅/KT 板/引导牌</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>各 2 备用</t>
+          <t>由佳玉拉第三方+洋洋得意定制</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F+佳玉</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>当日 10:00 测试</t>
+          <t>T-2（24h 起订）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>翻页器×4 / 备用电脑×1</t>
+          <t>桌牌</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>★ 不一定做（5/16 决议）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>T-1 检查</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>转接头/线材</t>
+          <t>★ 主讲台胸花（真花）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>HDMI/Type-C/Lightning 各 3</t>
+          <t>1 束 + 主讲嘉宾各 1（去年买重了）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F+王胜</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>T-1</t>
+          <t>T-1（按讲台尺寸定）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>对讲机</t>
+          <t>★ 讲台花（真花，按尺寸匹配）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>26 台（分 3 频道）</t>
+          <t>1 个（去年痛点：尺寸不对）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>A+E</t>
+          <t>F+洋洋得意</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>当日 09:00 分发</t>
+          <t>T-1</t>
         </is>
       </c>
     </row>
@@ -5093,400 +6146,778 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>★陈潇张江工厂灯光/舞台/音响</t>
+          <t>手持麦 ×6</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>1 套（自有资源）</t>
+          <t>会务公司+一滴水提供</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>T-1 进场（陈潇主导，节省赞助）</t>
+          <t>T-1 充电+T-0 试音</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像机</t>
+          <t>领夹麦 ×6</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>主机×2 游机×2</t>
+          <t>★ 可能没有则用手持替代</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>当日 11:00 调试</t>
+          <t>T-1 确认</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>直播推流设备</t>
+          <t>电脑</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>1 套（含备用 4G）</t>
+          <t>★ 会务公司 3-4 台 + 张卓自带备份</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>D+E</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>T-1 试推（直播确认开启）</t>
+          <t>T-1 跟班尼杨确认到底谁带</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>★地铁→场地快进短视频</t>
+          <t>翻页器</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>1 段 60 秒</t>
+          <t>会务公司带</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>D+F</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>T-5 拍摄完成、T-3 群发</t>
+          <t>T-1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>★交响乐往届预热视频</t>
+          <t>★ 对讲机（5/16 修正 26→10 台）</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>5-7 段 短视频</t>
+          <t>10 台（每组组长 1 台+C/E/G 多 1 台+机动）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+E</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>T-7 起视频号每日 1 条</t>
+          <t>T-0 当天租赁</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>茶歇（500人）</t>
+          <t>舞台 / 灯光（一滴水）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>高端冷餐/茶饮</t>
+          <t>★ 一滴水重新搭建，吴伟调试</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E 张卓</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>15:30 上桌</t>
+          <t>T-1 下午到场确认</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>伴手礼</t>
+          <t>陈潇张江工厂设备（补充）</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>VVIP/嘉宾/机构 3 档</t>
+          <t>灯光/音响（视一滴水是否够）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C+E</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>T-2 分装（前移）</t>
+          <t>按需调用</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>晚宴桌花/席位卡</t>
+          <t>摄影/摄像机</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>500 人 50 桌</t>
+          <t>主机 ×2 + 游机 ×2</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>18:00 前完成（晚宴名单 T-7 锁定）</t>
+          <t>当日 11:00 调试</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>★赞助物料（腾讯/华为）</t>
+          <t>★ 直播确认（待定）</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>按合同清单</t>
+          <t>★ 5/16 决议：大概率不直播</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D+葛九明</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>T-4 与品牌方对接确认（去年痛点）</t>
+          <t>T-3 最终确认</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>志愿者午餐+证书+纪念品</t>
+          <t>图文/文字传播</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>26 套</t>
+          <t>现场金句卡 + 朋友圈/小红书</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>A+F</t>
+          <t>D 蒋珊</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>T-1 分装、当日 12:00 发</t>
+          <t>T-0 实时发布</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>急救包/AED 标识</t>
+          <t>地铁→场地快进短视频</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2 套 / 全场 3 处</t>
+          <t>1 段 60 秒</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D+F</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>当日 09:00 就位</t>
+          <t>T-5 拍摄、T-3 群发嘉宾群</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>★急救主岗（蔡萍持证）</t>
+          <t>交响乐往届预热视频</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1 名</t>
+          <t>5-7 段短视频</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D 皮尔德</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>全程在 G 组指挥点待命</t>
+          <t>T-7 起视频号每日 1 条</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>后勤</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>应急联络卡（含对接清单）</t>
+          <t>★ 茶歇（盒马·林爱平）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>全员人手 1 张</t>
+          <t>500 人量（音乐会期间用）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>A+G</t>
+          <t>F+林爱平</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>T-3 发放（采纳张卓建议）</t>
+          <t>T-7 拉群打招呼+T-1 确认+T-0 送达</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>后勤</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>备用雨伞</t>
+          <t>★ 茶歇位置</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>100 把</t>
+          <t>★ 放门口（远离会场，解决去年噪音）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F+洋洋得意</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>视天气</t>
+          <t>T-0 布置</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>伴手礼</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>300+ 份，按赞助比例分配</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>T-1 头一天到+统一分装到袋（耗时 1-2h）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>晚宴喜卡/菜单/酒水/桌花</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>晚宴在一楼大厅</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>F+韦佳玉</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>T-1 准备+T-0 摆放</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>晚宴 LED 大屏 PPT 模板</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>★ 曲面长屏特殊尺寸</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>C+陈潇</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>T-3 找会务公司班尼杨做模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>★ 赞助物料（腾讯/华为/蔚来）</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>按合同清单</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>F 刘严+春子</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>T-4 与品牌方对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>刘总赞助酒水/饮料</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>异地发货（物流 2-3 天）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>F 刘严+刘总</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>T-5 前发货，收件人胡继刚</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>志愿者午餐+证书+纪念品</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>27 套</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>A+F</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>T-1 分装+当日 12:00 发</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>后勤</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>晚宴抽奖奖品（一/二/三等奖）</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>★ 5/16 新增</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉+赞助方</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>T-3 与赞助商确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>急救包/AED 标识</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>2 套 / 全场 3 处</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>当日 09:00 就位</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>★ 急救主岗（蔡萍持证）</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>1 名</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>全程在 G 组指挥点待命</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>应急联络卡（含对接清单）</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>全员人手 1 张</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>A+G</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>T-3 发放（张卓建议）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>★ 舞台周边安全岗</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>★ 舞台两边各 1 + 机动 2 / 半小时轮换</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>全场（5/16 刘严方案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>应急</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>备用雨伞</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>100 把</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>视天气</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>★T-2 嘉宾点对点提醒短信/微信</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>T-2 嘉宾点对点提醒短信/微信</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>全部嘉宾</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>T-2 18:00 前完成（采纳JasonCAI建议）</t>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>B+春子</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>T-2 18:00 前完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>★ 嘉宾名单 3 类（演讲/晚宴/总）</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>三表分管，到活动前可能调整</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>春子+B+F</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>T-7 V1+T-1 锁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>★ 前两排观众+发奖人提前通知</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>★ 5/16 陈潇方案</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>C 徐胜博</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>T-1 文档化发到群</t>
         </is>
       </c>
     </row>
@@ -5685,7 +7116,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>总策划指定升任：第三次参加经验最足，带 B 组</t>
+          <t>总策划指定升任：第三次参加经验最足，带 B 组；5/16 反馈需其他组临时调配支援</t>
         </is>
       </c>
     </row>
@@ -5729,7 +7160,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>VIP 1V1（主旨嘉宾）</t>
+          <t>VIP 1V1（主旨嘉宾）+ 引导动线</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5749,7 +7180,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>形象气质+审美佳，适合白硕、夏春等主旨嘉宾</t>
+          <t>扩职：主旨嘉宾 1V1 + 演讲嘉宾直接引导至第一排座位（不设贵宾室）</t>
         </is>
       </c>
     </row>
@@ -5761,7 +7192,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>观众席引导</t>
+          <t>观众席引导（待联系）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -5781,39 +7212,39 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>采纳冯墨建议补观众席引导盲区，新人友好岗</t>
+          <t>★5/16 王胜反馈：Angi 联系不上，需总策划侧确认或备选机动支援</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>动线引导</t>
+          <t>★ 执行总监 ② 会务方向 / C 组组长</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、核心搭子</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>标准引导岗</t>
+          <t>总策划设立双执行总监：陈潇分管会务执行方向（流程/舞台/设备/制作）；与韦佳玉并列向总策划负责</t>
         </is>
       </c>
     </row>
@@ -5825,12 +7256,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>★ 执行总监 ② 会务方向 / C 组组长</t>
+          <t>副组长 / 计时员</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -5840,12 +7271,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>广告活动一条龙、张江有自有灯光/舞台/音响工厂、核心搭子</t>
+          <t>中信证券，自报会务+倒计时</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>总策划设立双执行总监：陈潇分管会务执行方向（流程/舞台/设备/制作）；与韦佳玉并列向总策划负责</t>
+          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
         </is>
       </c>
     </row>
@@ -5857,27 +7288,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 计时员</t>
+          <t>主持对接/串场</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C/B → C</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>中信证券，自报会务+倒计时</t>
+          <t>私募→律师、时间灵活、沟通强</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
+          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
         </is>
       </c>
     </row>
@@ -5889,27 +7320,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>主持对接/串场</t>
+          <t>PPT/资料对接</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>C/B → C</t>
+          <t>B/C → C</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>私募→律师、时间灵活、沟通强</t>
+          <t>建筑设计+地产+养老研究、首次</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
+          <t>细致岗，提前 24h 收齐讲者 PPT</t>
         </is>
       </c>
     </row>
@@ -5921,27 +7352,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>B/C → C</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>建筑设计+地产+养老研究、首次</t>
+          <t>一二级创投、K12教育</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>细致岗，提前 24h 收齐讲者 PPT</t>
+          <t>创投背景对接颁奖机构得体</t>
         </is>
       </c>
     </row>
@@ -5953,27 +7384,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行/机构对接</t>
+          <t>圆桌/机构嘉宾对接（调入）</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B→E→C</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>一二级创投、K12教育</t>
+          <t>12级、投融资、教育/医疗/AI</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>创投背景对接颁奖机构得体</t>
+          <t>投融资人脉，对接 4 位圆桌嘉宾+主旨讲者上下场（技术非其专长，回归会务）</t>
         </is>
       </c>
     </row>
@@ -5985,27 +7416,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>圆桌/机构嘉宾对接（调入）</t>
+          <t>动线引导+前两排带位（调入）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>B→E→C</t>
+          <t>B → C</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>12级、投融资、教育/医疗/AI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>投融资人脉，对接 4 位圆桌嘉宾+主旨讲者上下场（技术非其专长，回归会务）</t>
+          <t>★5/16 从 B 调入 C：负责前 4 排席卡带位+圆桌嘉宾按席卡入座引导</t>
         </is>
       </c>
     </row>
@@ -6616,7 +8047,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>B - VIP 1V1（主旨嘉宾）</t>
+          <t>B - VIP 1V1（主旨嘉宾）+ 引导动线</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -6633,7 +8064,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B - 观众席引导</t>
+          <t>B - 观众席引导（待联系）</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -6650,12 +8081,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B - 动线引导</t>
+          <t>C - ★ 执行总监 ② 会务方向 / C 组组长</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>陈潇 Kelly</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -6667,12 +8098,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>C - ★ 执行总监 ② 会务方向 / C 组组长</t>
+          <t>C - 副组长 / 计时员</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly</t>
+          <t>王珏</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -6684,12 +8115,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C - 副组长 / 计时员</t>
+          <t>C - 主持对接/串场</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>冯墨 律师</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -6701,12 +8132,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C - 主持对接/串场</t>
+          <t>C - PPT/资料对接</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>冯墨 律师</t>
+          <t>黄璐 Lucius</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
@@ -6718,12 +8149,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C - PPT/资料对接</t>
+          <t>C - 颁奖执行/机构对接</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>黄璐 Lucius</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -6735,12 +8166,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C - 颁奖执行/机构对接</t>
+          <t>C - 圆桌/机构嘉宾对接（调入）</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -6752,12 +8183,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C - 圆桌/机构嘉宾对接（调入）</t>
+          <t>C - 动线引导+前两排带位（调入）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -7018,7 +8449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7582,6 +9013,546 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>王胜(5/16)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>嘉宾名单到活动前一天还在变化，需弹性预案</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>B+春子</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>三类名单（演讲/晚宴/总）分管，T-1 锁定 V2，预留 5% 空位</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>王胜(5/16)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>B 组实际剩 3 人需其他组临时调配</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>A+G</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>★ 启用 G 组机动调配 + 高峰时段 D/E 闲置志愿者顶岗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>王胜(5/16)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>演讲嘉宾直接落座第一排（不设贵宾室）</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>B+C</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>JasonCAI 升职责：演讲嘉宾直接引导至第一排席卡位</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰(5/16)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>茶歇位置往门口放（解决去年噪音）</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>★ 茶歇位置改放门口；远离会场入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰(5/16)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>盒马茶歇提前一周联系林爱平</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>T-7 建群打招呼；T-1 确认；T-0 送达</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>刘严(5/16)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>舞台周边安全分 4 区轮换（两侧+机动）</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>舞台两边各 1 人+机动 2 人；半小时轮换；4 人方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/16)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>电脑由会务公司带 3-4 台+自带备份</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>E+陈潇</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>T-1 跟班尼杨确认到底谁带；自备 1 台兜底</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/16)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>PPT 提前一天给组员熟悉</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>C 组收齐后 T-1 18:00 前给 E 组组员练手</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/16)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>停车/收费/货拉拉引导提前告知嘉宾</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>B+F</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>从洋洋得意拿到指引文档，T-3 群发</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>陈潇(5/16)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>颁奖嘉宾+前两排观众提前通知</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>★ 徐胜博整理文档；T-3 发到嘉宾群+点对点告知</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>陈潇(5/16)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>圆桌嘉宾席卡放位置+大屏 PPT 引导</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>席卡放主席台；圆桌单独 PPT 页（嘉宾照片+介绍）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>陈潇(5/16)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>晚宴节目供应商推荐+不搭台</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>陈潇+佳玉</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>用场地方现有台子；陈潇提供长期合作的节目供应商</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉(5/16)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>晚宴另一场地需志愿者监督预算</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>F+佳玉</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>保证嘉宾不额外点餐；费用在预算内</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉(5/16)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>名单/名牌/KT板/晚宴主图设计前置 1-2 天</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>F+佳玉</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>物料制作有排期；前置 24-48h 给设计方</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉(5/16)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>晚宴当天临时加位 → 允许（与之前预案不同）</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>调整后采纳</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>B+F</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>★ 推翻之前预案：去年也有 7-8 位临时加入；预留 1-2 桌</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚(5/16)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>入场标识改为 4 种手环+贴纸（替代 500 张胸牌）</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>下午嘉宾/工作人员 + 晚宴嘉宾/工作人员 4 种</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚(5/16)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>对讲机改 10 台（主要发组长，C/E/G 多 1 台）</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>A+E</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>★ 修正 v6 的 26 台方案；按需调配</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>彭常丽/盒马(5/16)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>音乐会安排在中场（不是后场）= 茶歇时间</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>C+F</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>茶歇与音乐会期间同步进行；F 组按音乐会时间上茶歇</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚(5/16)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>会议节奏：3 次全体+组长会穿插 2 次+组内 1-2 次</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>下周再开 2 次全体；组长会穿插 2 次；组内自行安排</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>葛九明缺席(5/16)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>D 组当天未到，单独沟通</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>待办</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>胡继刚私下与葛九明对接 D 组进度</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>

--- a/2026峰会_志愿者分工表.xlsx
+++ b/2026峰会_志愿者分工表.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>5 人</t>
+          <t>4 人</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>陈潇 Kelly（组长）</t>
+          <t>陈潇 Kelly（执行总监②）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>6 人</t>
+          <t>8 人</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>葛九明（组长）</t>
+          <t>葛九明（组长 · 南京远程）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>4 人</t>
+          <t>2 人</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>3 人</t>
+          <t>4 人</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>3 人</t>
+          <t>4 人</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>4 人</t>
+          <t>3 人</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>★ 晚宴抽奖奖品确认（一/二/三等奖）</t>
+          <t>★ 嘉宾 PPT 全部收齐（5-6 位主旨）→ 转交张卓</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉+赞助</t>
+          <t>C 黄璐</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>★ 节目供应商提案确认（陈潇推荐）</t>
+          <t>★ PPT 模板（空模板带尺寸）发给嘉宾</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>陈潇+韦佳玉</t>
+          <t>C 陈潇+黄璐</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>★ 前两排观众+发奖人提前通知文档化</t>
+          <t>★ 米兰达主持稿对接+嘉宾介绍发出</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>C 徐胜博</t>
+          <t>C 冯墨</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
+          <t>★ 全体第三次会议（讨论会议流程+人员缺席排除）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>全员</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
+          <t>★ 晚宴抽奖奖品确认（一/二/三等奖 7 桌）</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>韦佳玉+赞助</t>
         </is>
       </c>
     </row>
@@ -1350,299 +1350,435 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>短视频发主群+嘉宾群预热</t>
+          <t>★ 节目供应商提案确认（陈潇推荐 3 场节目）</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>陈潇+韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
+          <t>★ 前两排观众+发奖人提前通知文档化</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>B+春子</t>
+          <t>C 吕志翔+徐胜博</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>T-2 (5/20)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>现场踏勘 2（含彩排站位）</t>
+          <t>C 组致电每位讲者+主持人对发言时间（防超时）</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>A+C+E</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21) 下午</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>★ 现场踏勘 2 + 吴伟灯光位置确认 + 讲台尺寸量取</t>
+          <t>对接联系人清单（酒店/AV/餐饮/安保）发到全员</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>A+C+E+F+佳玉</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-3 (5/19)</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>全员线上彩排 18:00-19:30（1.5h）</t>
+          <t>短视频发主群+嘉宾群预热</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A+全员</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>★ 主讲台胸花+讲台花到货（按尺寸定制）</t>
+          <t>B 组 VIP 1V1 点对点短信/微信提醒嘉宾</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>F+王胜</t>
+          <t>B+春子</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>★ 伴手礼到货+统一分装到袋（1-2 小时）</t>
+          <t>现场踏勘 2（含彩排站位）</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>F+其他组支援</t>
+          <t>A+C+E</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>T-1 (5/21)</t>
+          <t>T-3 (5/19) 12:30</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>全设备压力测试+陈潇工厂设备进场（如需）</t>
+          <t>★ 全体明日中午现场踏勘（12:30-13:00 集合 看 3 块屏+三个场地）</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>A+所有组长</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>T-0 08:30</t>
+          <t>T-2 (5/20) 下午</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>★ 会务公司班尼杨设备入场（不需提前一天）</t>
+          <t>★ 周四下午彩排：主持人米兰达+技术组+设备一起对焦</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>E+班尼杨</t>
+          <t>C+E+米兰达</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>T-0 09:00</t>
+          <t>T-2 (5/20) 下午</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>★ A/F/G 三组到场：指挥部+物料布置+AED急救包就位</t>
+          <t>★ 张卓与场地方沟通：音乐厅灯光在音乐环节作用</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>A+F+G</t>
+          <t>E 张卓+一滴水吴伟</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>T-0 10:00</t>
+          <t>T-2 (5/20)</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>★ C 会务+E 技术到场：走台彩排+设备联调</t>
+          <t>★ 乐团需求确认（人数/弧形站位/30 把椅子）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>E 张卓+F 朱俊峰</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>T-0 11:00</t>
+          <t>T-1 (5/21) 下午</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>D 媒体到场：机位调试+直播试推流</t>
+          <t>★ 现场踏勘 2 + 讲台尺寸量取（如未量）</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A+F+佳玉</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>T-0 11:30</t>
+          <t>T-1 (5/21)</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>B 接待到场：签到台开台+VIP陪同上岗</t>
+          <t>全员线上彩排 18:00-19:30（1.5h）</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+全员</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>T-0 12:00</t>
+          <t>T-1 (5/21)</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>全员就位；VIP 车队首班；签到 13:00 开放</t>
+          <t>★ 主讲台胸花+讲台花到货（按尺寸定制）</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>全员</t>
+          <t>F+王胜</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>T-0 13:25</t>
+          <t>T-1 (5/21)</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>全员静默 5 分钟、广播开场倒计时</t>
+          <t>★ 伴手礼到货+统一分装到袋（1-2 小时）</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F+其他组支援</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>T-0 15:00</t>
+          <t>T-1 (5/21)</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>★ 晚宴专项人员到场：F/B/D/G 晚宴组分批进入晚宴厅</t>
+          <t>全设备压力测试+陈潇工厂设备进场（如需）</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>F+B+D+G</t>
+          <t>C+E</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>T-0 18:30</t>
+          <t>T-0 08:30</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>晚宴开席</t>
+          <t>★ 会务公司班尼杨设备入场（不需提前一天）</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>全员</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>T-0 09:00</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>★ A/F/G 三组到场：指挥部+物料布置+AED急救包就位</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>A+F+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>T-0 10:00</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>★ C 会务+E 技术到场：走台彩排+设备联调</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:00</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>D 媒体到场：机位调试+直播试推流</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>T-0 11:30</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>B 接待到场：签到台开台+VIP陪同上岗</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>T-0 12:00</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>全员就位；VIP 车队首班；签到 13:00 开放</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>T-0 13:25</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>全员静默 5 分钟、广播开场倒计时</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>T-0 15:00</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>★ 晚宴专项人员到场：F/B/D/G 晚宴组分批进入晚宴厅</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>F+B+D+G</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>T-0 18:30</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>晚宴开席</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
           <t>T+1</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>通稿次日 10:00 前发布、复盘会、问题归档</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>A+D</t>
         </is>
@@ -1861,7 +1997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2107,7 +2243,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>讲者 PPT/资料/换片</t>
+          <t>讲者 PPT 收集（5-6 位主旨）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2124,41 +2260,41 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>流程超时/嘉宾迟到</t>
+          <t>讲者 PPT 微调+现场播放</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>C 组 王珏（计时）</t>
+          <t>E 组 皮尔德小号（高晨）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>陈潇 → 韦佳玉</t>
+          <t>E 组 张卓</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>圆桌嘉宾上下场</t>
+          <t>流程超时/嘉宾迟到</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>C 组 吕志翔</t>
+          <t>C 组 王珏（计时）</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>陈潇 → 韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>颁奖物料/获奖嘉宾</t>
+          <t>圆桌一对接（AI硬核·王珏主持）</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2168,87 +2304,87 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>王珏</t>
+          <t>C 组 陈潇</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>法务/舆情/突发声明</t>
+          <t>圆桌二对接（投资·黄欣主持）</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>C 组 冯墨（律师）</t>
+          <t>C 组 马磊</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>E 组 张卓（律师）→ 胡继刚</t>
+          <t>C 组 陈潇</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>医疗/急救 ★</t>
+          <t>巅峰对话对接（云端·总策划主持）</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>G 组 蔡萍 ★</t>
+          <t>胡继刚</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>G 组 刘严</t>
+          <t>韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>跨组人手不足/机动调配</t>
+          <t>★ 颁奖物料/获奖嘉宾</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>G 组 刘严（组长）</t>
+          <t>C 组 吕志翔</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯 / 马磊</t>
+          <t>徐胜博</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>媒体应急口径</t>
+          <t>法务/舆情/突发声明</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>G 组 马磊</t>
+          <t>C 组 冯墨（律师）</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>D 组 葛九明</t>
+          <t>E 组 张卓（律师）→ 胡继刚</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>入场安检/可疑人员</t>
+          <t>医疗/急救 ★</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>G 组 康诺斯</t>
+          <t>G 组 蔡萍 ★</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2260,219 +2396,270 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>交响乐团对接</t>
+          <t>跨组人手不足/机动调配</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>F 组 朱俊峰</t>
+          <t>G 组 刘严（组长）</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉（去年负责）</t>
+          <t>G 组 康诺斯 / 马磊</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>晚宴席位/敬酒/现场对接</t>
+          <t>媒体应急口径</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>F 组 Winny</t>
+          <t>G 组 马磊</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>B 组 王胜</t>
+          <t>D 组 葛九明</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>嘉宾邀约确认/全程跟进</t>
+          <t>入场安检/可疑人员</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>A 组 春子</t>
+          <t>G 组 康诺斯</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉 → 胡继刚</t>
+          <t>G 组 刘严</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>赞助资源/物料落位</t>
+          <t>交响乐团对接</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>A 组 春子</t>
+          <t>F 组 朱俊峰</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>F 组 朱俊峰 → 胡继刚</t>
+          <t>韦佳玉（去年负责）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>议程脚本/会议记录/复盘</t>
+          <t>晚宴席位/敬酒/现场对接</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>A 组 韦佳玉</t>
+          <t>F 组 Winny</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>胡继刚</t>
+          <t>B 组 王胜</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>无法解决/重大决策</t>
+          <t>嘉宾邀约确认/全程跟进</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
+          <t>A 组 春子</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
           <t>韦佳玉 → 胡继刚</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>会务公司（舞台/道具/音响）</t>
+          <t>赞助资源/物料落位</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>班尼杨 312（C 陈潇主对接）</t>
+          <t>A 组 春子</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>E 张卓</t>
+          <t>F 组 朱俊峰 → 胡继刚</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>白天主持人/串场对接</t>
+          <t>议程脚本/会议记录/复盘</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>米兰达（吕苗苗）→ 陈潇</t>
+          <t>A 组 韦佳玉</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉</t>
+          <t>胡继刚</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>场地/停车/讲台尺寸/胸花尺寸</t>
+          <t>无法解决/重大决策</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>洋洋得意（一滴水物业）</t>
+          <t>韦佳玉 → 胡继刚</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>F 朱俊峰</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>茶歇（盒马）</t>
+          <t>会务公司（舞台/道具/音响）</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>林爱平（F 朱俊峰拉群）</t>
+          <t>班尼杨 312（C 陈潇主对接）</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>彭常丽</t>
+          <t>E 张卓</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>一滴水灯光</t>
+          <t>白天主持人/串场对接</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>吴伟（E 张卓 21 号下午对接）</t>
+          <t>米兰达（吕苗苗）→ 陈潇</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>随圣博</t>
+          <t>韦佳玉</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>赞助酒水/饮料（异地发货）</t>
+          <t>场地/停车/讲台尺寸/胸花尺寸</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>刘总（F 刘严对接）</t>
+          <t>洋洋得意（一滴水物业）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>春子</t>
+          <t>F 朱俊峰</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
+          <t>茶歇（盒马）</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>林爱平（F 朱俊峰拉群）</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>彭常丽</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>一滴水灯光</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>吴伟（E 张卓 21 号下午对接）</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>随圣博</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>赞助酒水/饮料（异地发货）</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>刘总（F 刘严对接）</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>春子</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>晚宴 PM</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>韦佳玉（兼任）</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>陈潇</t>
         </is>
@@ -2632,12 +2819,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>蒋珊</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>A 角总策划指定；B 角自媒体+摄影核心岗</t>
+          <t>A 角总策划指定（南京远程）；B 角 AI 内容+前期宣发主力</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2846,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>A 角律师协调统筹；B 角技术执行（操作设备）</t>
+          <t>A 角律师协调统筹；B 角技术执行+PPT 微调由皮尔德负责</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2868,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>A 角建筑+协会运营；B 角空窗期时间最多+零售运营</t>
+          <t>A 角建筑+协会运营+物料；B 角茶歇晚宴主管；张蒙调入协助</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2890,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>A 角统筹机动调配；B 角持急救证常驻医疗岗★</t>
+          <t>A 角舞台安全+机动；B 角持急救证常驻医疗岗★；马磊已调出至 C</t>
         </is>
       </c>
     </row>
@@ -5851,7 +6038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6011,12 +6198,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>★ 志愿者专用橙色胸牌</t>
+          <t>★ 志愿者胸牌（5/18 修正：不写名字）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>27 张（含韦佳玉）</t>
+          <t>27 张'志愿者'字样；单一颜色与工作牌区分</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -6026,7 +6213,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>T-2 完成（张蒙建议）</t>
+          <t>★5/18 决议：志愿者不需要名单，统一'志愿者'字样</t>
         </is>
       </c>
     </row>
@@ -6038,22 +6225,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>横幅/KT 板/引导牌</t>
+          <t>★ 二维码核销单（打印 6-8 份）</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>由佳玉拉第三方+洋洋得意定制</t>
+          <t>★ 不做立牌（5/18 节省成本）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>F+佳玉</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>T-2（24h 起订）</t>
+          <t>T-2 打印</t>
         </is>
       </c>
     </row>
@@ -6065,22 +6252,22 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>桌牌</t>
+          <t>横幅/KT 板/引导牌</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>★ 不一定做（5/16 决议）</t>
+          <t>由佳玉拉第三方+洋洋得意定制</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F+佳玉</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>T-2（24h 起订）</t>
         </is>
       </c>
     </row>
@@ -6092,22 +6279,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>★ 主讲台胸花（真花）</t>
+          <t>桌牌</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>1 束 + 主讲嘉宾各 1（去年买重了）</t>
+          <t>★ 不一定做（5/16 决议）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>F+王胜</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>T-1（按讲台尺寸定）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6119,49 +6306,49 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>★ 讲台花（真花，按尺寸匹配）</t>
+          <t>★ 主讲台胸花（真花）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>1 个（去年痛点：尺寸不对）</t>
+          <t>1 束 + 主讲嘉宾各 1（去年买重了）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>F+洋洋得意</t>
+          <t>F+王胜</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>T-1</t>
+          <t>T-1（按讲台尺寸定）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>技术</t>
+          <t>会务</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>手持麦 ×6</t>
+          <t>★ 讲台花（真花，按尺寸匹配）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>会务公司+一滴水提供</t>
+          <t>1 个（去年痛点：尺寸不对）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>E+班尼杨</t>
+          <t>F+洋洋得意</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>T-1 充电+T-0 试音</t>
+          <t>T-1</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6360,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>领夹麦 ×6</t>
+          <t>手持麦 ×6</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>★ 可能没有则用手持替代</t>
+          <t>会务公司+一滴水提供</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -6188,7 +6375,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>T-1 确认</t>
+          <t>T-1 充电+T-0 试音</t>
         </is>
       </c>
     </row>
@@ -6200,22 +6387,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>电脑</t>
+          <t>领夹麦 ×6</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>★ 会务公司 3-4 台 + 张卓自带备份</t>
+          <t>★ 可能没有则用手持替代</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>T-1 跟班尼杨确认到底谁带</t>
+          <t>T-1 确认</t>
         </is>
       </c>
     </row>
@@ -6227,22 +6414,22 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>翻页器</t>
+          <t>电脑</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>会务公司带</t>
+          <t>★ 会务公司 3-4 台 + 张卓自带备份</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>E+班尼杨</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>T-1</t>
+          <t>T-1 跟班尼杨确认到底谁带</t>
         </is>
       </c>
     </row>
@@ -6254,22 +6441,22 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>★ 对讲机（5/16 修正 26→10 台）</t>
+          <t>翻页器</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>10 台（每组组长 1 台+C/E/G 多 1 台+机动）</t>
+          <t>会务公司带</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>A+E</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>T-0 当天租赁</t>
+          <t>T-1</t>
         </is>
       </c>
     </row>
@@ -6281,22 +6468,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>舞台 / 灯光（一滴水）</t>
+          <t>★ 对讲机 10 台（5/18 确认：会务公司提供）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>★ 一滴水重新搭建，吴伟调试</t>
+          <t>10 台（每组组长 1 台+C/E/G 多 1 台+机动）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>E 张卓</t>
+          <t>A+E+班尼杨</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>T-1 下午到场确认</t>
+          <t>T-0 当天送达（去年清单上无对讲机，今年新增）</t>
         </is>
       </c>
     </row>
@@ -6308,76 +6495,76 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陈潇张江工厂设备（补充）</t>
+          <t>★ 备用无线话筒 ×2</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>灯光/音响（视一滴水是否够）</t>
+          <t>去年 4 台基础上 +2</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>C+E</t>
+          <t>E+班尼杨</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>按需调用</t>
+          <t>T-0 当天送达</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>摄影/摄像机</t>
+          <t>舞台 / 灯光（一滴水）</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>主机 ×2 + 游机 ×2</t>
+          <t>★ 一滴水重新搭建，吴伟调试</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E 张卓</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>当日 11:00 调试</t>
+          <t>T-1 下午到场确认</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>技术</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>★ 直播确认（待定）</t>
+          <t>陈潇张江工厂设备（补充）</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>★ 5/16 决议：大概率不直播</t>
+          <t>灯光/音响（视一滴水是否够）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>D+葛九明</t>
+          <t>C+E</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>T-3 最终确认</t>
+          <t>按需调用</t>
         </is>
       </c>
     </row>
@@ -6389,22 +6576,22 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>图文/文字传播</t>
+          <t>摄影/摄像机</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>现场金句卡 + 朋友圈/小红书</t>
+          <t>主机 ×2 + 游机 ×2</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>D 蒋珊</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>T-0 实时发布</t>
+          <t>当日 11:00 调试</t>
         </is>
       </c>
     </row>
@@ -6416,22 +6603,22 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>地铁→场地快进短视频</t>
+          <t>★ 直播确认（待定）</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1 段 60 秒</t>
+          <t>★ 5/16 决议：大概率不直播</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>D+F</t>
+          <t>D+葛九明</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>T-5 拍摄、T-3 群发嘉宾群</t>
+          <t>T-3 最终确认</t>
         </is>
       </c>
     </row>
@@ -6443,76 +6630,76 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>交响乐往届预热视频</t>
+          <t>图文/文字传播</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>5-7 段短视频</t>
+          <t>现场金句卡 + 朋友圈/小红书</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>D 皮尔德</t>
+          <t>D 蒋珊</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>T-7 起视频号每日 1 条</t>
+          <t>T-0 实时发布</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>★ 茶歇（盒马·林爱平）</t>
+          <t>地铁→场地快进短视频</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>500 人量（音乐会期间用）</t>
+          <t>1 段 60 秒</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>F+林爱平</t>
+          <t>D+F</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>T-7 拉群打招呼+T-1 确认+T-0 送达</t>
+          <t>T-5 拍摄、T-3 群发嘉宾群</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>后勤</t>
+          <t>媒体</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>★ 茶歇位置</t>
+          <t>交响乐往届预热视频</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>★ 放门口（远离会场，解决去年噪音）</t>
+          <t>5-7 段短视频</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>F+洋洋得意</t>
+          <t>D 皮尔德</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>T-0 布置</t>
+          <t>T-7 起视频号每日 1 条</t>
         </is>
       </c>
     </row>
@@ -6524,22 +6711,22 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>伴手礼</t>
+          <t>★ 茶歇（盒马·林爱平）</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>300+ 份，按赞助比例分配</t>
+          <t>500 人量（音乐会期间用）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>F+林爱平</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>T-1 头一天到+统一分装到袋（耗时 1-2h）</t>
+          <t>T-7 拉群打招呼+T-1 确认+T-0 送达</t>
         </is>
       </c>
     </row>
@@ -6551,22 +6738,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>晚宴喜卡/菜单/酒水/桌花</t>
+          <t>★ 茶歇位置</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>晚宴在一楼大厅</t>
+          <t>★ 放门口（远离会场，解决去年噪音）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>F+韦佳玉</t>
+          <t>F+洋洋得意</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>T-1 准备+T-0 摆放</t>
+          <t>T-0 布置</t>
         </is>
       </c>
     </row>
@@ -6578,22 +6765,22 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>晚宴 LED 大屏 PPT 模板</t>
+          <t>伴手礼</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>★ 曲面长屏特殊尺寸</t>
+          <t>300+ 份，按赞助比例分配</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>C+陈潇</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>T-3 找会务公司班尼杨做模板</t>
+          <t>T-1 头一天到+统一分装到袋（耗时 1-2h）</t>
         </is>
       </c>
     </row>
@@ -6605,22 +6792,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>★ 赞助物料（腾讯/华为/蔚来）</t>
+          <t>晚宴喜卡/菜单/酒水/桌花</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>按合同清单</t>
+          <t>晚宴在一楼大厅</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>F 刘严+春子</t>
+          <t>F+韦佳玉</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>T-4 与品牌方对接</t>
+          <t>T-1 准备+T-0 摆放</t>
         </is>
       </c>
     </row>
@@ -6632,22 +6819,22 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>刘总赞助酒水/饮料</t>
+          <t>晚宴 LED 大屏 PPT 模板</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>异地发货（物流 2-3 天）</t>
+          <t>★ 曲面长屏特殊尺寸</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>F 刘严+刘总</t>
+          <t>C+陈潇</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>T-5 前发货，收件人胡继刚</t>
+          <t>T-3 找会务公司班尼杨做模板</t>
         </is>
       </c>
     </row>
@@ -6659,22 +6846,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>志愿者午餐+证书+纪念品</t>
+          <t>★ 赞助物料（腾讯/华为/蔚来）</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>27 套</t>
+          <t>按合同清单</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>A+F</t>
+          <t>F 刘严+春子</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>T-1 分装+当日 12:00 发</t>
+          <t>T-4 与品牌方对接</t>
         </is>
       </c>
     </row>
@@ -6686,76 +6873,76 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>晚宴抽奖奖品（一/二/三等奖）</t>
+          <t>刘总赞助酒水/饮料</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>★ 5/16 新增</t>
+          <t>异地发货（物流 2-3 天）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>韦佳玉+赞助方</t>
+          <t>F 刘严+刘总</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>T-3 与赞助商确认</t>
+          <t>T-5 前发货，收件人胡继刚</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>后勤</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>急救包/AED 标识</t>
+          <t>志愿者午餐+证书+纪念品</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2 套 / 全场 3 处</t>
+          <t>27 套</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A+F</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>当日 09:00 就位</t>
+          <t>T-1 分装+当日 12:00 发</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>应急</t>
+          <t>后勤</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>★ 急救主岗（蔡萍持证）</t>
+          <t>晚宴抽奖奖品（一/二/三等奖）</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>1 名</t>
+          <t>★ 5/16 新增</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>韦佳玉+赞助方</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>全程在 G 组指挥点待命</t>
+          <t>T-3 与赞助商确认</t>
         </is>
       </c>
     </row>
@@ -6767,22 +6954,22 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>应急联络卡（含对接清单）</t>
+          <t>急救包/AED 标识</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>全员人手 1 张</t>
+          <t>2 套 / 全场 3 处</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>A+G</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>T-3 发放（张卓建议）</t>
+          <t>当日 09:00 就位</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6981,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>★ 舞台周边安全岗</t>
+          <t>★ 急救主岗（蔡萍持证）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>★ 舞台两边各 1 + 机动 2 / 半小时轮换</t>
+          <t>1 名</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -6809,7 +6996,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>全场（5/16 刘严方案）</t>
+          <t>全程在 G 组指挥点待命</t>
         </is>
       </c>
     </row>
@@ -6821,76 +7008,76 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>备用雨伞</t>
+          <t>应急联络卡（含对接清单）</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>100 把</t>
+          <t>全员人手 1 张</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A+G</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>视天气</t>
+          <t>T-3 发放（张卓建议）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>应急</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>T-2 嘉宾点对点提醒短信/微信</t>
+          <t>★ 舞台周边安全岗</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>全部嘉宾</t>
+          <t>★ 舞台两边各 1 + 机动 2 / 半小时轮换</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>B+春子</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>T-2 18:00 前完成</t>
+          <t>全场（5/16 刘严方案）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>应急</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>★ 嘉宾名单 3 类（演讲/晚宴/总）</t>
+          <t>备用雨伞</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>三表分管，到活动前可能调整</t>
+          <t>100 把</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>春子+B+F</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>T-7 V1+T-1 锁定</t>
+          <t>视天气</t>
         </is>
       </c>
     </row>
@@ -6902,22 +7089,238 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>T-2 嘉宾点对点提醒短信/微信</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>全部嘉宾</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>B+春子</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>T-2 18:00 前完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>★ 嘉宾名单 3 类（演讲/晚宴/总）</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>三表分管，到活动前可能调整</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>春子+B+F</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>T-7 V1+T-1 锁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>★ 前两排观众+发奖人提前通知</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>★ 5/16 陈潇方案</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>C 徐胜博</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>T-1 文档化发到群</t>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>5/16 陈潇方案 + 5/18 吕志翔主导</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>C 吕志翔</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>T-3 文档化发到群</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>★ PPT 模板 5 份（带 B/A 厅尺寸）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>空白模板带尺寸 → 嘉宾按模板做</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>C 陈潇+黄璐</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>T-3 发给 5-6 位主旨嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>场地</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>★ B 厅 2 块主屏（主旨演讲）</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>尺寸已群发；两屏中间有门隔开</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>5/18 已发到 26 人群</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>场地</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>★ A 厅 L 型曲面屏（晚宴）</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>约 20m × 2m 长曲面屏</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>F+韦佳玉</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>会务公司班尼杨做 2-3 页 PPT 模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>场地</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>★ 3 楼场地（今年不动）</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>去年用 3 楼今年不动</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>已知信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>财务</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>★ 发票需求：餐饮+会务物料</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>全部要发票</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Benny.Y 提供费用清单后再制作</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>财务</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>★ 发票需求：茶歇不需要</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>保留购物小票即可</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>F+Winny</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>盒马采购</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7679,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>保留计时核心岗（自荐），副组长稳定流程节奏</t>
+          <t>保留计时核心岗（自荐）；按主时间纵线举牌 5/3/1min</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7691,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>主持对接/串场</t>
+          <t>★ 主持人对接+主持稿协助</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -7308,7 +7711,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>律师沟通力+时间灵活，最适合协调主持脚本</t>
+          <t>★5/18 扩职：嘉宾介绍/出场顺序/控场倒计时/帮主持人完善主持稿；与米兰达一对一对接</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7723,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>PPT/资料对接</t>
+          <t>★ PPT 收集主责人</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -7340,7 +7743,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>细致岗，提前 24h 收齐讲者 PPT</t>
+          <t>★5/18 明确：黄璐为 PPT 收集主责（只收 5-6 位主旨嘉宾 PPT；圆桌无 PPT）；转交给 E 组张卓</t>
         </is>
       </c>
     </row>
@@ -7352,27 +7755,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>颁奖执行/机构对接</t>
+          <t>★ 颁奖执行（主导）</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B→E→C → ★颁奖</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>一二级创投、K12教育</t>
+          <t>12级、投融资、教育/医疗/AI</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>创投背景对接颁奖机构得体</t>
+          <t>★5/18 总策划指令：吕志翔升任颁奖主导；投融资人脉对接颁奖机构最得体</t>
         </is>
       </c>
     </row>
@@ -7384,27 +7787,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>圆桌/机构嘉宾对接（调入）</t>
+          <t>圆桌一对接（AI 硬核）</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>B→E→C</t>
+          <t>未明示</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>12级、投融资、教育/医疗/AI</t>
+          <t>一二级创投、K12教育</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>投融资人脉，对接 4 位圆桌嘉宾+主旨讲者上下场（技术非其专长，回归会务）</t>
+          <t>原颁奖岗转：对接圆桌一（王珏主持，4 位嘉宾上下场+席卡）</t>
         </is>
       </c>
     </row>
@@ -7416,59 +7819,59 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>动线引导+前两排带位（调入）</t>
+          <t>★ 圆桌二对接（投资）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>马磊</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>★G → C</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>AI Club 生态、跨界资源</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>★5/18 总策划指令：从 G 应急组调入 C；AI 圈层人脉+跨界资源最适合对接投资圆桌（黄欣主持）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>动线引导+前 4 排带位</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>B → C</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>★5/16 从 B 调入 C：负责前 4 排席卡带位+圆桌嘉宾按席卡入座引导</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>组长</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>葛九明</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>—（总策划指定）</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>媒体/宣传背景（待补全）</t>
-        </is>
-      </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>总策划指定 D 组组长，统筹摄影摄像/直播/新媒体/媒体接待对外口径</t>
+          <t>5/16 从 B 调入 C：前 4 排席卡带位+圆桌嘉宾按席卡入座引导</t>
         </is>
       </c>
     </row>
@@ -7480,27 +7883,27 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 摄影摄像+自媒体</t>
+          <t>组长（南京远程指挥）</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>—（总策划指定）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>大宗行/AI数据中心、本身做自媒体</t>
+          <t>媒体/宣传背景（待补全）</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>保留摄影摄像与自媒体核心岗，作为 D 组副组长</t>
+          <t>★5/18 决议：葛九明确认自己+小团队可完成 D 组工作；常在南京远程指挥</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7915,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AI 内容/新媒体</t>
+          <t>AI 内容/新媒体+前期宣发</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -7532,39 +7935,39 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>AI 圈层资源最强；新媒体（金句卡/朋友圈/小红书）</t>
+          <t>★扩职：AI 圈层资源+朋友圈/相关群预热宣发+活动海报推广；现场金句卡新媒体即时发布</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>直播+交响乐预热+媒体接待</t>
+          <t>组长 / 协调统筹</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>皮尔德小号</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>未明示</t>
+          <t>B/G → E</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>互联网 10 年→城市更新、资源对接强</t>
+          <t>财税律师、二次参加、协调能力强</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>扩职：原马磊的媒体接待并入；主管直播+交响乐往届视频 T-7 起视频号每日预热</t>
+          <t>律师协调能力强，统筹 E 组与场馆 AV 外包/陈潇工厂设备；★5/18 已与杨帆（班尼杨）/吴伟（灯光）对接</t>
         </is>
       </c>
     </row>
@@ -7576,27 +7979,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>组长 / 协调统筹（调入）</t>
+          <t>副组长 / 现场音响+话筒</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>随圣博 Joshua-Sui</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>B/G → E</t>
+          <t>B/E/G → E</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>财税律师、二次参加、协调能力强</t>
+          <t>复旦管院年会后勤经验</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>总策划指定：律师协调能力强，统筹 E 组与场馆 AV 外包/陈潇工厂设备</t>
+          <t>嘉宾上场递话筒/换备用机/收回关麦；故障第一时间报告组长</t>
         </is>
       </c>
     </row>
@@ -7608,27 +8011,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 技术执行</t>
+          <t>★ PPT 播放+微调（调入）</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>随圣博 Joshua-Sui</t>
+          <t>皮尔德小号（高晨）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>B/E/G → E</t>
+          <t>D → E（重心）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>复旦管院年会后勤经验</t>
+          <t>互联网 10 年→城市更新、资源对接强</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>技术执行核心，对接场馆 AV 现场操作</t>
+          <t>★5/18 调整：从 D 调入 E 主岗；负责 PPT 微调（字号/排序/兼容性）+ 现场播放；周三晚收齐+预留半天微调</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8063,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>标准化对接执行</t>
+          <t>标准化对接执行；对讲机/转接头/线材就位</t>
         </is>
       </c>
     </row>
@@ -7672,7 +8075,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>组长 / 场地+物料+赞助物料</t>
+          <t>组长 / 物料+伴手礼+赞助物料</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -7692,7 +8095,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>扩职：原刘严的赞助物料对接并入；建筑+协会运营经验主导场地与物料</t>
+          <t>★5/18 扩职：物料制作（与 Benny.Y 班尼杨对接费用清单）+ 嘉宾席卡（向胡继刚/韦佳玉拿名单）+ 赞助物料</t>
         </is>
       </c>
     </row>
@@ -7704,7 +8107,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 茶歇+晚宴主管（调入）</t>
+          <t>副组长 / 茶歇+晚宴主管</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -7724,7 +8127,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>★最适合茶歇/晚宴：空窗期时间最多+零售运营+商务接待经验；从 B 调入做副组长</t>
+          <t>★最适合茶歇/晚宴：空窗期时间最多+零售运营+商务接待经验；★5/18 待办：与佳玉对接志愿者午餐/纪念品/证书预算</t>
         </is>
       </c>
     </row>
@@ -7736,7 +8139,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>茶歇+晚宴专员</t>
+          <t>晚宴对接专员</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -7756,39 +8159,39 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>去年已熟悉流程，副手 Winny 主管 500 人茶歇+晚宴对接</t>
+          <t>★5/18 明确职责：晚宴环节对接（席位/菜单/酒水/桌花/敬酒流程）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>组长 / 安保+机动调配（调入）</t>
+          <t>茶歇执行+协助物料（调入）</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>F → G</t>
+          <t>D → F</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>自报积极、平日接活多、协调力强</t>
+          <t>大宗行/AI数据中心、本身做自媒体</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>总策划指定：从 F 副组长调任 G 组长，统筹安保+机动跨组调配</t>
+          <t>★5/18 总策划指令：从 D 组调入 F 组（F 缺人）；协助朱俊峰物料+Winny 茶歇</t>
         </is>
       </c>
     </row>
@@ -7800,27 +8203,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>副组长 / 急救+医疗主岗 ★</t>
+          <t>组长 / 舞台安全+机动调配</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>B/G → G</t>
+          <t>F → G</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>复旦经院培训负责人(退休)、★持有急救证</t>
+          <t>自报积极、平日接活多、协调力强</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>升任副组长；保留急救/医疗专项岗（持证稀缺技能）</t>
+          <t>★5/18 重点方向：舞台周边安全（两侧各 1 人+机动 2 人/半小时轮换）+入场安检辅助+可疑人员主动询问+舆情口径与 D 组联动</t>
         </is>
       </c>
     </row>
@@ -7832,27 +8235,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>机动 / 媒体应急口径（调入）</t>
+          <t>副组长 / 急救+医疗主岗 ★</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>D → G</t>
+          <t>B/G → G</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>AI Club 生态、跨界资源</t>
+          <t>复旦经院培训负责人(退休)、★持有急救证</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>媒体应急口径+跨界资源；G 组机动支援</t>
+          <t>升任副组长；保留急救/医疗专项岗（持证稀缺技能）</t>
         </is>
       </c>
     </row>
@@ -7864,7 +8267,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>机动 / 安保</t>
+          <t>机动 / 安保+入场安检</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -7884,7 +8287,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>保留 G 组（自选偏好），机动支援+入场安检</t>
+          <t>★5/18 重申：应急机动组分工预案已部署完毕；机动支援+入场安检+可疑人员</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8518,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>C - 主持对接/串场</t>
+          <t>C - ★ 主持人对接+主持稿协助</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -8132,7 +8535,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C - PPT/资料对接</t>
+          <t>C - ★ PPT 收集主责人</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -8149,12 +8552,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C - 颁奖执行/机构对接</t>
+          <t>C - ★ 颁奖执行（主导）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>徐胜博</t>
+          <t>吕志翔</t>
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
@@ -8166,12 +8569,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C - 圆桌/机构嘉宾对接（调入）</t>
+          <t>C - 圆桌一对接（AI 硬核）</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>吕志翔</t>
+          <t>徐胜博</t>
         </is>
       </c>
       <c r="C16" s="5" t="n"/>
@@ -8183,12 +8586,12 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>C - 动线引导+前两排带位（调入）</t>
+          <t>C - ★ 圆桌二对接（投资）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>马磊</t>
         </is>
       </c>
       <c r="C17" s="5" t="n"/>
@@ -8200,12 +8603,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>D - 组长</t>
+          <t>C - 动线引导+前 4 排带位</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>葛九明</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
@@ -8217,12 +8620,12 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>D - 副组长 / 摄影摄像+自媒体</t>
+          <t>D - 组长（南京远程指挥）</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>张蒙 AEGISTAR</t>
+          <t>葛九明</t>
         </is>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -8234,7 +8637,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>D - AI 内容/新媒体</t>
+          <t>D - AI 内容/新媒体+前期宣发</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -8251,12 +8654,12 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>D - 直播+交响乐预热+媒体接待</t>
+          <t>E - 组长 / 协调统筹</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>皮尔德小号</t>
+          <t>张卓 盈科</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -8268,12 +8671,12 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>E - 组长 / 协调统筹（调入）</t>
+          <t>E - 副组长 / 现场音响+话筒</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>张卓 盈科</t>
+          <t>随圣博 Joshua-Sui</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -8285,12 +8688,12 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>E - 副组长 / 技术执行</t>
+          <t>E - ★ PPT 播放+微调（调入）</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>随圣博 Joshua-Sui</t>
+          <t>皮尔德小号（高晨）</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -8319,7 +8722,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>F - 组长 / 场地+物料+赞助物料</t>
+          <t>F - 组长 / 物料+伴手礼+赞助物料</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -8336,7 +8739,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>F - 副组长 / 茶歇+晚宴主管（调入）</t>
+          <t>F - 副组长 / 茶歇+晚宴主管</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -8353,7 +8756,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>F - 茶歇+晚宴专员</t>
+          <t>F - 晚宴对接专员</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -8370,12 +8773,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>G - 组长 / 安保+机动调配（调入）</t>
+          <t>F - 茶歇执行+协助物料（调入）</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>刘严</t>
+          <t>张蒙 AEGISTAR</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -8387,12 +8790,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>G - 副组长 / 急救+医疗主岗 ★</t>
+          <t>G - 组长 / 舞台安全+机动调配</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>蔡萍</t>
+          <t>刘严</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -8404,12 +8807,12 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>G - 机动 / 媒体应急口径（调入）</t>
+          <t>G - 副组长 / 急救+医疗主岗 ★</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>马磊</t>
+          <t>蔡萍</t>
         </is>
       </c>
       <c r="C30" s="5" t="n"/>
@@ -8421,7 +8824,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>G - 机动 / 安保</t>
+          <t>G - 机动 / 安保+入场安检</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -8449,7 +8852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9553,6 +9956,546 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>总策划(5/18)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>★ 吕志翔接管颁奖执行（升任主导）</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>原徐胜博转岗对接圆桌一；吕志翔投融资人脉对接颁奖机构最得体</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>总策划(5/18)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>★ 圆桌二对接从 G 组调一人</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>G→C</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>马磊 G→C：AI Club 生态+跨界资源最适合对接投资圆桌（黄欣主持）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>陈潇(5/18)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>PPT 模板由 C 组制作（不只给比例数字）</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>陈潇+黄璐做空模板带尺寸（B厅/A厅 屏幕尺寸已群发）发给嘉宾</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>黄璐(5/18)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>明确 PPT 收集人 = 黄璐 → E 张卓</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>周三前全部收齐 5-6 位主旨嘉宾 PPT；圆桌无 PPT 不需要</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>所有节点提前到周三晚（不是周四）</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>★ 留 24h 缓冲；deadline 不是 0:00 而是周三晚收口</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>米兰达(5/18)</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>周四下午彩排（主持人+技术组+设备）</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>C+E</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>周四下午婚宴场地大概率空着；备选周五上午</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/18)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>乐团弧形布局，无法在主舞台 → 安排侧面</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>E+F</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>需 30 把椅子（F 朱俊峰协助搬运）；张卓与乐团联系人单独对接</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/18)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>对讲机 10 台由会务公司提供（非新采购）</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>去年清单+对讲机 10 台+备用无线话筒 ×2；领夹麦确认是否要</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰(5/18)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>物料制作需 Benny.Y 先给费用清单后再制作</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>餐饮+会务物料要发票；茶歇不要发票（保留小票）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>朱俊峰(5/18)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>二维码核销单打印 6-8 份（不做立牌）</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>★ 节省成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>志愿者用'志愿者'胸牌（不写名字）+ 工作牌用不同颜色</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>嘉宾席卡+晚宴名单+工作人员名单→ 向胡继刚/韦佳玉拿</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>场地三个厅全部打通（场地方大力支持）</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>确认</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>B 厅 ×2 主屏 = 主旨演讲；A 厅 L 型曲面屏 20m×2m = 晚宴；3 楼今年不动</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>晚宴 7 桌 + 3 场节目 + 抽奖环节</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>韦佳玉</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>晚宴 PM 韦佳玉；陈潇推荐节目供应商；不搭台（用场地方现有）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>米兰达暂定晚宴主持人</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>暂定</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>待与姚老师商量；若同意则单独与米兰达沟通晚宴流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>张蒙 D→F（F 组缺人；葛九明自己能搞定 D）</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>D→F</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>张蒙协助朱俊峰物料+Winny 茶歇</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>皮尔德小号（高晨）重心 D→E</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>D→E</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>高晨负责放 PPT+预留半天微调；葛九明自带小团队搞 D 组</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>参加 2 次以上的企业当天发证书</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>F+佳玉</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Winny 与佳玉对接预算/选择范围/确认流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>各组长收集组员联系方式+人员替换</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>各组长</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>当天来不了的及时替换；其他组志愿者高峰时段可调配支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Aiden(5/18)</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>明日（5/19）12:30 全体现场踏勘</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>采纳</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>★ 看 3 块屏+三个场地；F+G 组与酒店工作人员沟通晚宴保障</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>张卓(5/18)</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>音乐厅灯光在音乐环节是否可用 → 周四确认</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>待办</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>张卓周四下午到现场与场地方沟通</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
